--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_21oct26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_21oct26_Wed.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3829" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="363">
   <si>
     <t>Date</t>
   </si>
@@ -1299,7 +1299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1515,14 +1515,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1826,7 +1829,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P982"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1888,220 +1890,224 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>46281.416666666664</v>
+    <row r="2" spans="1:16" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>706</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-31.78743961</v>
+        <v>21.82490752</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5">
-        <v>1035</v>
+        <v>2027.5</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="L2" s="17">
-        <v>17940</v>
-      </c>
-      <c r="M2" s="17">
-        <f>ABS((D2*E2)-L2)</f>
-        <v>10880</v>
-      </c>
-      <c r="N2" s="10" t="str">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B2, $C$2:$C$628, C2, $D$2:$D$628, D2, $E$2:$E$628, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>46281.416666666664</v>
+      <c r="P2" s="22"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
-        <v>726</v>
+        <v>2435</v>
       </c>
       <c r="F3" s="4">
-        <v>-29.855072459999999</v>
+        <v>20.09864365</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="H3" s="5">
-        <v>1035</v>
+        <v>2027.5</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="L3" s="17">
-        <v>17940</v>
-      </c>
-      <c r="M3" s="17">
-        <f>ABS((D3*E3)-L3)</f>
-        <v>10680</v>
-      </c>
-      <c r="N3" s="10" t="str">
+      <c r="J3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B3, $C$2:$C$628, C3, $D$2:$D$628, D3, $E$2:$E$628, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>61</v>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4">
-        <v>660</v>
+        <v>204</v>
       </c>
       <c r="F4" s="4">
-        <v>-20.625375829999999</v>
+        <v>17.477685000000001</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5">
-        <v>831.5</v>
+        <v>173.65</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" t="str">
+      <c r="K4" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="L4" s="17">
+        <v>10550</v>
+      </c>
+      <c r="M4" s="17">
+        <f>ABS((D4*E4)-L4)</f>
+        <v>350</v>
+      </c>
+      <c r="N4" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B4, $C$2:$C$628, C4, $D$2:$D$628, D4, $E$2:$E$628, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>61</v>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>46275.457638888889</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E5" s="4">
-        <v>2560</v>
+        <v>222</v>
       </c>
       <c r="F5" s="4">
-        <v>-17.071590539999999</v>
+        <v>13.892879130000001</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="H5" s="5">
-        <v>3087</v>
+        <v>194.92</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" t="str">
+      <c r="K5" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="L5" s="17">
+        <v>56375</v>
+      </c>
+      <c r="M5" s="17">
+        <f>ABS((D5*E5)-L5)</f>
+        <v>34175</v>
+      </c>
+      <c r="N5" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B5, $C$2:$C$628, C5, $D$2:$D$628, D5, $E$2:$E$628, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>46268.385416666664</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5">
-        <v>640</v>
+      <c r="D6" s="4">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4">
+        <v>214</v>
       </c>
       <c r="F6" s="4">
-        <v>-16.883116879999999</v>
+        <v>9.7886312330000003</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="H6" s="5">
-        <v>770</v>
+        <v>194.92</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>323</v>
+        <v>229</v>
       </c>
       <c r="L6" s="17">
-        <v>3450</v>
+        <v>21900</v>
       </c>
       <c r="M6" s="17">
         <f>ABS((D6*E6)-L6)</f>
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="N6" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B6, $C$2:$C$628, C6, $D$2:$D$628, D6, $E$2:$E$628, E6) &gt; 1, "Duplicate", "Unique")</f>
@@ -2110,47 +2116,40 @@
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="42">
-        <v>46304.388888888891</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="7" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="5">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5">
-        <v>2105</v>
+      <c r="D7" s="4">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4">
+        <v>212</v>
       </c>
       <c r="F7" s="4">
-        <v>-16.76551997</v>
+        <v>8.7625692589999993</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5">
-        <v>2529</v>
+        <v>194.92</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="L7" s="17">
-        <v>19395</v>
-      </c>
-      <c r="M7" s="17">
-        <f>ABS((D7*E7)-L7)</f>
-        <v>450</v>
-      </c>
+      <c r="J7" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
       <c r="N7" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B7, $C$2:$C$628, C7, $D$2:$D$628, D7, $E$2:$E$628, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -2158,47 +2157,40 @@
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="42">
-        <v>46304.387499999997</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="8" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>46252.645138888889</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5">
-        <v>500</v>
-      </c>
-      <c r="E8" s="5">
-        <v>30.3</v>
+      <c r="D8" s="4">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4">
+        <v>401</v>
       </c>
       <c r="F8" s="4">
-        <v>-15.763135950000001</v>
+        <v>8.0280172410000006</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5">
-        <v>35.97</v>
+        <v>371.2</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="L8" s="17">
-        <v>15850</v>
-      </c>
-      <c r="M8" s="17">
-        <f>ABS((D8*E8)-L8)</f>
-        <v>700</v>
-      </c>
+      <c r="J8" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
       <c r="N8" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B8, $C$2:$C$628, C8, $D$2:$D$628, D8, $E$2:$E$628, E8) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -2206,142 +2198,124 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42">
-        <v>46308.578472222223</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    <row r="9" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5">
-        <v>13</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1209</v>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3888</v>
       </c>
       <c r="F9" s="4">
-        <v>-15.11023733</v>
+        <v>6.9306930690000002</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="H9" s="5">
-        <v>1424.2</v>
+        <v>3636</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="L9" s="17">
-        <v>17017</v>
-      </c>
-      <c r="M9" s="17">
-        <f>ABS((D9*E9)-L9)</f>
-        <v>1300</v>
-      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
       <c r="N9" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B9, $C$2:$C$628, C9, $D$2:$D$628, D9, $E$2:$E$628, E9) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O9" s="10"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42">
-        <v>46308.538888888892</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    <row r="10" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5">
-        <v>8</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2155</v>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3856</v>
       </c>
       <c r="F10" s="4">
-        <v>-14.788453929999999</v>
+        <v>6.0506050609999997</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" s="5">
-        <v>2529</v>
+        <v>3636</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="L10" s="17">
-        <v>18040</v>
-      </c>
-      <c r="M10" s="17">
-        <f>ABS((D10*E10)-L10)</f>
-        <v>800</v>
-      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
       <c r="N10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B10, $C$2:$C$628, C10, $D$2:$D$628, D10, $E$2:$E$628, E10) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O10" s="10"/>
+      <c r="O10" s="18"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
+    <row r="11" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>46283.375</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="5">
-        <v>5</v>
-      </c>
-      <c r="E11" s="5">
-        <v>660</v>
+      <c r="D11" s="4">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4">
+        <v>870.2</v>
       </c>
       <c r="F11" s="4">
-        <v>-14.28571429</v>
+        <v>5.9926918389999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H11" s="5">
-        <v>770</v>
+        <v>821</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="L11" s="17">
-        <v>3550</v>
+        <v>17920</v>
       </c>
       <c r="M11" s="17">
         <f>ABS((D11*E11)-L11)</f>
-        <v>250</v>
+        <v>516</v>
       </c>
       <c r="N11" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B11, $C$2:$C$628, C11, $D$2:$D$628, D11, $E$2:$E$628, E11) &gt; 1, "Duplicate", "Unique")</f>
@@ -2350,113 +2324,119 @@
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>61</v>
+    <row r="12" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4">
-        <v>2660</v>
+        <v>870</v>
       </c>
       <c r="F12" s="4">
-        <v>-13.83219955</v>
+        <v>5.9683313030000003</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H12" s="5">
-        <v>3087</v>
+        <v>821</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" t="str">
+      <c r="J12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="17">
+        <v>17700</v>
+      </c>
+      <c r="M12" s="17">
+        <f>ABS((D12*E12)-L12)</f>
+        <v>300</v>
+      </c>
+      <c r="N12" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B12, $C$2:$C$628, C12, $D$2:$D$628, D12, $E$2:$E$628, E12) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42">
-        <v>46308.536805555559</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="O12" s="10"/>
+      <c r="P12" s="22"/>
+    </row>
+    <row r="13" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5">
-        <v>200</v>
-      </c>
-      <c r="E13" s="5">
-        <v>31.1</v>
+      <c r="D13" s="4">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4">
+        <v>206</v>
       </c>
       <c r="F13" s="4">
-        <v>-13.53906033</v>
+        <v>5.6843833369999999</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H13" s="5">
-        <v>35.97</v>
+        <v>194.92</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="L13" s="17">
-        <v>6580</v>
-      </c>
-      <c r="M13" s="17">
-        <f>ABS((D13*E13)-L13)</f>
-        <v>360</v>
-      </c>
+      <c r="J13" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
       <c r="N13" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B13, $C$2:$C$628, C13, $D$2:$D$628, D13, $E$2:$E$628, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O13"/>
+      <c r="P13"/>
+    </row>
+    <row r="14" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>4014</v>
+        <v>3830</v>
       </c>
       <c r="F14" s="4">
-        <v>-12.45365322</v>
+        <v>5.3355335530000003</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="H14" s="5">
-        <v>4585</v>
+        <v>3636</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -2469,15 +2449,13 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B14, $C$2:$C$628, C14, $D$2:$D$628, D14, $E$2:$E$628, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O14"/>
-      <c r="P14"/>
-    </row>
-    <row r="15" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
-        <v>46031.4375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
@@ -2486,154 +2464,139 @@
         <v>3</v>
       </c>
       <c r="E15" s="4">
-        <v>1052</v>
+        <v>1302</v>
       </c>
       <c r="F15" s="4">
-        <v>-12.26753398</v>
+        <v>5.2376333659999998</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="H15" s="5">
-        <v>1199.0999999999999</v>
+        <v>1237.2</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="M15" s="17">
-        <f>ABS((D15*E15)-L15)</f>
-        <v>3156</v>
-      </c>
-      <c r="N15" s="10" t="str">
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B15, $C$2:$C$628, C15, $D$2:$D$628, D15, $E$2:$E$628, E15) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P15" s="18"/>
-    </row>
-    <row r="16" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42">
-        <v>46314.375</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="O15"/>
+      <c r="P15"/>
+    </row>
+    <row r="16" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="5">
-        <v>5</v>
-      </c>
-      <c r="E16" s="5">
-        <v>680</v>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3810</v>
       </c>
       <c r="F16" s="4">
-        <v>-11.688311690000001</v>
+        <v>4.7854785480000004</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="H16" s="5">
-        <v>770</v>
+        <v>3636</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="L16" s="17">
-        <v>3650</v>
-      </c>
-      <c r="M16" s="17">
-        <f>ABS((D16*E16)-L16)</f>
-        <v>250</v>
-      </c>
+      <c r="J16" s="33"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
       <c r="N16" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B16, $C$2:$C$628, C16, $D$2:$D$628, D16, $E$2:$E$628, E16) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42">
-        <v>46310.40347222222</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="2" t="s">
+    <row r="17" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>46252.635416666664</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="5">
-        <v>300</v>
-      </c>
-      <c r="E17" s="5">
-        <v>32.01</v>
+      <c r="D17" s="4">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4">
+        <v>850</v>
       </c>
       <c r="F17" s="4">
-        <v>-11.009174310000001</v>
+        <v>3.5322777099999998</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="H17" s="5">
-        <v>35.97</v>
+        <v>821</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="L17" s="17">
-        <v>10263</v>
-      </c>
-      <c r="M17" s="17">
-        <f>ABS((D17*E17)-L17)</f>
-        <v>660</v>
-      </c>
-      <c r="N17" s="10" t="str">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B17, $C$2:$C$628, C17, $D$2:$D$628, D17, $E$2:$E$628, E17) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" s="22" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>61</v>
+      <c r="P17"/>
+    </row>
+    <row r="18" spans="1:16" s="22" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E18" s="4">
-        <v>2752</v>
+        <v>122</v>
       </c>
       <c r="F18" s="4">
-        <v>-10.85195983</v>
+        <v>3.337286126</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H18" s="5">
-        <v>3087</v>
+        <v>118.06</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="33" t="s">
+      <c r="J18" s="34" t="s">
         <v>40</v>
       </c>
       <c r="K18" s="16"/>
@@ -2643,33 +2606,33 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B18, $C$2:$C$628, C18, $D$2:$D$628, D18, $E$2:$E$628, E18) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O18"/>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E19" s="4">
-        <v>4164</v>
+        <v>1277</v>
       </c>
       <c r="F19" s="4">
-        <v>-9.1821155940000008</v>
+        <v>3.2169414810000001</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H19" s="5">
-        <v>4585</v>
+        <v>1237.2</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
@@ -2685,35 +2648,37 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E20" s="4">
-        <v>4415</v>
+        <v>836</v>
       </c>
       <c r="F20" s="4">
-        <v>-9.0515820700000003</v>
+        <v>1.8270401949999999</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5">
-        <v>4854.3999999999996</v>
+        <v>821</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="33"/>
+      <c r="J20" s="33" t="s">
+        <v>40</v>
+      </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
@@ -2724,117 +2689,119 @@
       <c r="O20"/>
       <c r="P20"/>
     </row>
-    <row r="21" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42">
-        <v>46314.375</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
+    <row r="21" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>46254.375</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="5">
-        <v>11</v>
-      </c>
-      <c r="E21" s="5">
-        <v>701</v>
+      <c r="D21" s="4">
+        <v>7</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2230</v>
       </c>
       <c r="F21" s="4">
-        <v>-8.9610389609999999</v>
+        <v>1.6362061889999999</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5">
-        <v>770</v>
+        <v>2194.1</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="L21" s="17">
-        <v>8239</v>
-      </c>
-      <c r="M21" s="17">
-        <f>ABS((D21*E21)-L21)</f>
-        <v>528</v>
-      </c>
-      <c r="N21" t="str">
+      <c r="J21" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B21, $C$2:$C$628, C21, $D$2:$D$628, D21, $E$2:$E$628, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="O21"/>
+      <c r="P21"/>
+    </row>
+    <row r="22" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="42">
+        <v>46301.393055555556</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="4">
-        <v>4</v>
-      </c>
-      <c r="E22" s="4">
-        <v>701</v>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>19550</v>
       </c>
       <c r="F22" s="4">
-        <v>-8.4736910820000002</v>
+        <v>1.510981879</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H22" s="5">
-        <v>765.9</v>
+        <v>19259</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" t="str">
+      <c r="K22" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="L22" s="17">
+        <v>20020</v>
+      </c>
+      <c r="M22" s="17">
+        <f>ABS((D22*E22)-L22)</f>
+        <v>470</v>
+      </c>
+      <c r="N22" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B22, $C$2:$C$628, C22, $D$2:$D$628, D22, $E$2:$E$628, E22) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O22"/>
-      <c r="P22"/>
-    </row>
-    <row r="23" spans="1:16" s="22" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:16" s="22" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E23" s="4">
-        <v>4456</v>
+        <v>119</v>
       </c>
       <c r="F23" s="4">
-        <v>-8.206987475</v>
+        <v>0.79620531930000005</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H23" s="5">
-        <v>4854.3999999999996</v>
+        <v>118.06</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
@@ -2848,32 +2815,32 @@
         <v>Unique</v>
       </c>
       <c r="O23"/>
-      <c r="P23"/>
-    </row>
-    <row r="24" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
-        <v>46286.375</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="42">
+        <v>46311.595833333333</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="4">
-        <v>5</v>
-      </c>
-      <c r="E24" s="4">
-        <v>702</v>
+      <c r="D24" s="5">
+        <v>20</v>
+      </c>
+      <c r="E24" s="5">
+        <v>271</v>
       </c>
       <c r="F24" s="4">
-        <v>-6.7729083670000003</v>
+        <v>0.64995357470000004</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H24" s="5">
-        <v>753</v>
+        <v>269.25</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
@@ -2882,50 +2849,52 @@
         <v>40</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="L24" s="17">
-        <f>7470/2</f>
-        <v>3735</v>
+        <f>20*283</f>
+        <v>5660</v>
       </c>
       <c r="M24" s="17">
         <f>ABS((D24*E24)-L24)</f>
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="N24" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B24, $C$2:$C$628, C24, $D$2:$D$628, D24, $E$2:$E$628, E24) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="25" spans="1:16" s="27" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>46252.635416666664</v>
+    <row r="25" spans="1:16" s="27" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4">
-        <v>2892</v>
+        <v>4010</v>
       </c>
       <c r="F25" s="4">
-        <v>-6.3168124389999996</v>
+        <v>0.43580624150000002</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H25" s="5">
-        <v>3087</v>
+        <v>3992.6</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="33"/>
+      <c r="J25" s="33" t="s">
+        <v>40</v>
+      </c>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
@@ -2933,38 +2902,40 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B25, $C$2:$C$628, C25, $D$2:$D$628, D25, $E$2:$E$628, E25) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O25"/>
-      <c r="P25"/>
-    </row>
-    <row r="26" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26" s="4">
-        <v>18052</v>
+        <v>1614</v>
       </c>
       <c r="F26" s="4">
-        <v>-6.2671997509999997</v>
+        <v>0.37313432839999999</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H26" s="5">
-        <v>19259</v>
+        <v>1608</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="59"/>
+      <c r="J26" s="75" t="s">
+        <v>40</v>
+      </c>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
@@ -2975,90 +2946,110 @@
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="1" t="s">
+    <row r="27" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="42">
+        <v>46301.375694444447</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4">
-        <v>4560</v>
+      <c r="D27" s="5">
+        <v>5</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1664</v>
       </c>
       <c r="F27" s="4">
-        <v>-6.0646011870000001</v>
+        <v>0.36793533989999999</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="H27" s="5">
-        <v>4854.3999999999996</v>
+        <v>1657.9</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="59"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" t="str">
+      <c r="J27" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="L27" s="17">
+        <f>5*1752</f>
+        <v>8760</v>
+      </c>
+      <c r="M27" s="17">
+        <f>ABS((D27*E27)-L27)</f>
+        <v>440</v>
+      </c>
+      <c r="N27" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B27, $C$2:$C$628, C27, $D$2:$D$628, D27, $E$2:$E$628, E27) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O27"/>
-      <c r="P27"/>
-    </row>
-    <row r="28" spans="1:16" s="26" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" s="26" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="4">
-        <v>100</v>
-      </c>
-      <c r="E28" s="4">
-        <v>111</v>
+      <c r="D28" s="5">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>746</v>
       </c>
       <c r="F28" s="4">
-        <v>-5.9800101640000003</v>
+        <v>-0.92961487379999996</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="H28" s="5">
-        <v>118.06</v>
+        <v>753</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="59"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" t="str">
+      <c r="J28" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="L28" s="17">
+        <f>5*773</f>
+        <v>3865</v>
+      </c>
+      <c r="M28" s="17">
+        <f>ABS((D28*E28)-L28)</f>
+        <v>135</v>
+      </c>
+      <c r="N28" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B28, $C$2:$C$628, C28, $D$2:$D$628, D28, $E$2:$E$628, E28) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O28"/>
-      <c r="P28"/>
-    </row>
-    <row r="29" spans="1:16" s="70" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>61</v>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" s="70" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
@@ -3067,16 +3058,16 @@
         <v>25</v>
       </c>
       <c r="E29" s="4">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="F29" s="4">
-        <v>-5.4613935969999998</v>
+        <v>-1.0622154779999999</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="H29" s="5">
-        <v>265.5</v>
+        <v>329.5</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
@@ -3094,12 +3085,12 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" s="71" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" s="71" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="42">
-        <v>46311.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
@@ -3108,16 +3099,16 @@
         <v>5</v>
       </c>
       <c r="E30" s="5">
-        <v>712</v>
+        <v>620</v>
       </c>
       <c r="F30" s="4">
-        <v>-5.4448871179999996</v>
+        <v>-1.1400781310000001</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="H30" s="5">
-        <v>753</v>
+        <v>627.15</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
@@ -3126,14 +3117,14 @@
         <v>40</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="L30" s="17">
-        <v>3810</v>
+        <v>3395</v>
       </c>
       <c r="M30" s="17">
         <f>ABS((D30*E30)-L30)</f>
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="N30" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B30, $C$2:$C$628, C30, $D$2:$D$628, D30, $E$2:$E$628, E30) &gt; 1, "Duplicate", "Unique")</f>
@@ -3142,46 +3133,46 @@
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="1:16" s="73" customFormat="1" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" s="73" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="42">
-        <v>46303.375</v>
+        <v>46300.375694444447</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>273</v>
+        <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>1294</v>
+        <v>4510</v>
       </c>
       <c r="F31" s="4">
-        <v>-5.1806257789999997</v>
+        <v>-1.6357688109999999</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>275</v>
+        <v>97</v>
       </c>
       <c r="H31" s="5">
-        <v>1364.7</v>
+        <v>4585</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="58" t="s">
-        <v>40</v>
+      <c r="J31" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="L31" s="17">
-        <v>2852</v>
+        <v>4763</v>
       </c>
       <c r="M31" s="17">
         <f>ABS((D31*E31)-L31)</f>
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="N31" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B31, $C$2:$C$628, C31, $D$2:$D$628, D31, $E$2:$E$628, E31) &gt; 1, "Duplicate", "Unique")</f>
@@ -3190,37 +3181,35 @@
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="1:16" s="71" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" s="71" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E32" s="4">
-        <v>4364</v>
+        <v>116</v>
       </c>
       <c r="F32" s="4">
-        <v>-4.8200654309999997</v>
+        <v>-1.7448754870000001</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H32" s="5">
-        <v>4585</v>
+        <v>118.06</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="60" t="s">
-        <v>40</v>
-      </c>
+      <c r="J32" s="43"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
@@ -3231,76 +3220,76 @@
       <c r="O32"/>
       <c r="P32"/>
     </row>
-    <row r="33" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="56">
-        <v>46309</v>
+    <row r="33" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="42">
+        <v>46310.375</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E33" s="5">
-        <v>4640</v>
+        <v>315.10000000000002</v>
       </c>
       <c r="F33" s="4">
-        <v>-4.416611734</v>
+        <v>-2.1428571430000001</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="H33" s="5">
-        <v>4854.3999999999996</v>
+        <v>322</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="L33" s="17">
-        <v>4940</v>
+        <v>32200</v>
       </c>
       <c r="M33" s="17">
         <f>ABS((D33*E33)-L33)</f>
-        <v>300</v>
+        <v>689.99999999999636</v>
       </c>
       <c r="N33" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B33, $C$2:$C$628, C33, $D$2:$D$628, D33, $E$2:$E$628, E33) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="E34" s="4">
-        <v>1751</v>
+        <v>115.25</v>
       </c>
       <c r="F34" s="4">
-        <v>-4.3169398909999996</v>
+        <v>-2.3801456889999999</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="H34" s="5">
-        <v>1830</v>
+        <v>118.06</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
@@ -3316,30 +3305,30 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
-        <v>46302.468055555553</v>
+        <v>46121.375</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="4">
-        <v>3110</v>
+        <v>1614</v>
       </c>
       <c r="F35" s="4">
-        <v>-4.2576116739999996</v>
+        <v>-2.6479281019999998</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H35" s="5">
-        <v>3248.3</v>
+        <v>1657.9</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
@@ -3348,275 +3337,275 @@
         <v>40</v>
       </c>
       <c r="K35" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="L35" s="17">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M35" s="17">
+        <f>ABS((D35*E35)-L35)</f>
+        <v>540</v>
+      </c>
+      <c r="N35" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B35, $C$2:$C$628, C35, $D$2:$D$628, D35, $E$2:$E$628, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O35"/>
+      <c r="P35"/>
+    </row>
+    <row r="36" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="42">
+        <v>46311.595833333333</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="5">
+        <v>10</v>
+      </c>
+      <c r="E36" s="5">
+        <v>261</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-3.0640668519999998</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" s="5">
+        <v>269.25</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="L36" s="17">
+        <f>10*283</f>
+        <v>2830</v>
+      </c>
+      <c r="M36" s="17">
+        <f>ABS((D36*E36)-L36)</f>
+        <v>220</v>
+      </c>
+      <c r="N36" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B36, $C$2:$C$628, C36, $D$2:$D$628, D36, $E$2:$E$628, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="55" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="5">
+        <v>5</v>
+      </c>
+      <c r="E37" s="5">
+        <v>726</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-3.5856573709999999</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H37" s="5">
+        <v>753</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="L37" s="17">
+        <f>5*773</f>
+        <v>3865</v>
+      </c>
+      <c r="M37" s="17">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>235</v>
+      </c>
+      <c r="N37" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B37, $C$2:$C$628, C37, $D$2:$D$628, D37, $E$2:$E$628, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+    </row>
+    <row r="38" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>18552</v>
+      </c>
+      <c r="F38" s="4">
+        <v>-3.6710109559999999</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="5">
+        <v>19259</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" s="59"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B38, $C$2:$C$628, C38, $D$2:$D$628, D38, $E$2:$E$628, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O38"/>
+      <c r="P38"/>
+    </row>
+    <row r="39" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="42">
+        <v>46289.375</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="5">
+        <v>5</v>
+      </c>
+      <c r="E39" s="5">
+        <v>601</v>
+      </c>
+      <c r="F39" s="4">
+        <v>-4.1696563820000003</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H39" s="5">
+        <v>627.15</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="17">
+        <v>3245</v>
+      </c>
+      <c r="M39" s="17">
+        <f>ABS((D39*E39)-L39)</f>
+        <v>240</v>
+      </c>
+      <c r="N39" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B39, $C$2:$C$628, C39, $D$2:$D$628, D39, $E$2:$E$628, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>46302.468055555553</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
+        <v>3110</v>
+      </c>
+      <c r="F40" s="4">
+        <v>-4.2576116739999996</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" s="5">
+        <v>3248.3</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K40" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L40" s="17">
         <f>2*3334</f>
         <v>6668</v>
       </c>
-      <c r="M35" s="17">
-        <f>ABS((D35*E35)-L35)</f>
-        <v>448</v>
-      </c>
-      <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B35, $C$2:$C$628, C35, $D$2:$D$628, D35, $E$2:$E$628, E35) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-    </row>
-    <row r="36" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42">
-        <v>46289.375</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="5">
-        <v>5</v>
-      </c>
-      <c r="E36" s="5">
-        <v>601</v>
-      </c>
-      <c r="F36" s="4">
-        <v>-4.1696563820000003</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H36" s="5">
-        <v>627.15</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="L36" s="17">
-        <v>3245</v>
-      </c>
-      <c r="M36" s="17">
-        <f>ABS((D36*E36)-L36)</f>
-        <v>240</v>
-      </c>
-      <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B36, $C$2:$C$628, C36, $D$2:$D$628, D36, $E$2:$E$628, E36) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="55" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4">
-        <v>18552</v>
-      </c>
-      <c r="F37" s="4">
-        <v>-3.6710109559999999</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H37" s="5">
-        <v>19259</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="59"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B37, $C$2:$C$628, C37, $D$2:$D$628, D37, $E$2:$E$628, E37) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O37"/>
-      <c r="P37"/>
-    </row>
-    <row r="38" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="5">
-        <v>5</v>
-      </c>
-      <c r="E38" s="5">
-        <v>726</v>
-      </c>
-      <c r="F38" s="4">
-        <v>-3.5856573709999999</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="5">
-        <v>753</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J38" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K38" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="L38" s="17">
-        <f>5*773</f>
-        <v>3865</v>
-      </c>
-      <c r="M38" s="17">
-        <f>ABS((D38*E38)-L38)</f>
-        <v>235</v>
-      </c>
-      <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B38, $C$2:$C$628, C38, $D$2:$D$628, D38, $E$2:$E$628, E38) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="42">
-        <v>46311.595833333333</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="5">
-        <v>10</v>
-      </c>
-      <c r="E39" s="5">
-        <v>261</v>
-      </c>
-      <c r="F39" s="4">
-        <v>-3.0640668519999998</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H39" s="5">
-        <v>269.25</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J39" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="L39" s="17">
-        <f>10*283</f>
-        <v>2830</v>
-      </c>
-      <c r="M39" s="17">
-        <f>ABS((D39*E39)-L39)</f>
-        <v>220</v>
-      </c>
-      <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B39, $C$2:$C$628, C39, $D$2:$D$628, D39, $E$2:$E$628, E39) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3">
-        <v>46121.375</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="4">
-        <v>3</v>
-      </c>
-      <c r="E40" s="4">
-        <v>1614</v>
-      </c>
-      <c r="F40" s="4">
-        <v>-2.6479281019999998</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H40" s="5">
-        <v>1657.9</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J40" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="K40" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="L40" s="17">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
       <c r="M40" s="17">
         <f>ABS((D40*E40)-L40)</f>
-        <v>540</v>
+        <v>448</v>
       </c>
       <c r="N40" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B40, $C$2:$C$628, C40, $D$2:$D$628, D40, $E$2:$E$628, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E41" s="4">
-        <v>115.25</v>
+        <v>1751</v>
       </c>
       <c r="F41" s="4">
-        <v>-2.3801456889999999</v>
+        <v>-4.3169398909999996</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H41" s="5">
-        <v>118.06</v>
+        <v>1830</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
@@ -3632,81 +3621,83 @@
       <c r="O41"/>
       <c r="P41"/>
     </row>
-    <row r="42" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42">
-        <v>46310.375</v>
+    <row r="42" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="56">
+        <v>46309</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5">
-        <v>315.10000000000002</v>
+        <v>4640</v>
       </c>
       <c r="F42" s="4">
-        <v>-2.1428571430000001</v>
+        <v>-4.416611734</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="H42" s="5">
-        <v>322</v>
+        <v>4854.3999999999996</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J42" s="58" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="L42" s="17">
-        <v>32200</v>
+        <v>4940</v>
       </c>
       <c r="M42" s="17">
         <f>ABS((D42*E42)-L42)</f>
-        <v>689.99999999999636</v>
+        <v>300</v>
       </c>
       <c r="N42" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B42, $C$2:$C$628, C42, $D$2:$D$628, D42, $E$2:$E$628, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E43" s="4">
-        <v>116</v>
+        <v>4364</v>
       </c>
       <c r="F43" s="4">
-        <v>-1.7448754870000001</v>
+        <v>-4.8200654309999997</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H43" s="5">
-        <v>118.06</v>
+        <v>4585</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="43"/>
+      <c r="J43" s="60" t="s">
+        <v>40</v>
+      </c>
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
@@ -3717,58 +3708,58 @@
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="42">
-        <v>46300.375694444447</v>
+        <v>46303.375</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>12</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5">
-        <v>4510</v>
+        <v>1294</v>
       </c>
       <c r="F44" s="4">
-        <v>-1.6357688109999999</v>
+        <v>-5.1806257789999997</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>97</v>
+        <v>275</v>
       </c>
       <c r="H44" s="5">
-        <v>4585</v>
+        <v>1364.7</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="17" t="s">
-        <v>117</v>
+      <c r="J44" s="58" t="s">
+        <v>40</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="L44" s="17">
-        <v>4763</v>
+        <v>2852</v>
       </c>
       <c r="M44" s="17">
         <f>ABS((D44*E44)-L44)</f>
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="N44" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B44, $C$2:$C$628, C44, $D$2:$D$628, D44, $E$2:$E$628, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="45" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42">
-        <v>46295.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
@@ -3777,16 +3768,16 @@
         <v>5</v>
       </c>
       <c r="E45" s="5">
-        <v>620</v>
+        <v>712</v>
       </c>
       <c r="F45" s="4">
-        <v>-1.1400781310000001</v>
+        <v>-5.4448871179999996</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="H45" s="5">
-        <v>627.15</v>
+        <v>753</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
@@ -3795,14 +3786,14 @@
         <v>40</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="L45" s="17">
-        <v>3395</v>
+        <v>3810</v>
       </c>
       <c r="M45" s="17">
         <f>ABS((D45*E45)-L45)</f>
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="N45" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B45, $C$2:$C$628, C45, $D$2:$D$628, D45, $E$2:$E$628, E45) &gt; 1, "Duplicate", "Unique")</f>
@@ -3811,12 +3802,12 @@
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
     </row>
-    <row r="46" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3">
-        <v>46252.6875</v>
+    <row r="46" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
@@ -3825,16 +3816,16 @@
         <v>25</v>
       </c>
       <c r="E46" s="4">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="F46" s="4">
-        <v>-1.0622154779999999</v>
+        <v>-5.4613935969999998</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="H46" s="5">
-        <v>329.5</v>
+        <v>265.5</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
@@ -3852,131 +3843,113 @@
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="2" t="s">
+    <row r="47" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="5">
-        <v>5</v>
-      </c>
-      <c r="E47" s="5">
-        <v>746</v>
+      <c r="D47" s="4">
+        <v>100</v>
+      </c>
+      <c r="E47" s="4">
+        <v>111</v>
       </c>
       <c r="F47" s="4">
-        <v>-0.92961487379999996</v>
+        <v>-5.9800101640000003</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="H47" s="5">
-        <v>753</v>
+        <v>118.06</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="L47" s="17">
-        <f>5*773</f>
-        <v>3865</v>
-      </c>
-      <c r="M47" s="17">
-        <f>ABS((D47*E47)-L47)</f>
-        <v>135</v>
-      </c>
-      <c r="N47" s="10" t="str">
+      <c r="J47" s="59"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B47, $C$2:$C$628, C47, $D$2:$D$628, D47, $E$2:$E$628, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="42">
-        <v>46301.375694444447</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="O47"/>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="5">
-        <v>5</v>
-      </c>
-      <c r="E48" s="5">
-        <v>1664</v>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4">
+        <v>4560</v>
       </c>
       <c r="F48" s="4">
-        <v>0.36793533989999999</v>
+        <v>-6.0646011870000001</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="H48" s="5">
-        <v>1657.9</v>
+        <v>4854.3999999999996</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="L48" s="17">
-        <f>5*1752</f>
-        <v>8760</v>
-      </c>
-      <c r="M48" s="17">
-        <f>ABS((D48*E48)-L48)</f>
-        <v>440</v>
-      </c>
-      <c r="N48" s="10" t="str">
+      <c r="J48" s="59"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B48, $C$2:$C$628, C48, $D$2:$D$628, D48, $E$2:$E$628, E48) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O48"/>
+      <c r="P48"/>
+    </row>
+    <row r="49" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4">
-        <v>1614</v>
+        <v>18052</v>
       </c>
       <c r="F49" s="4">
-        <v>0.37313432839999999</v>
+        <v>-6.2671997509999997</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H49" s="5">
-        <v>1608</v>
+        <v>19259</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="76" t="s">
-        <v>40</v>
-      </c>
+      <c r="J49" s="59"/>
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
@@ -3987,37 +3960,35 @@
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
-        <v>61</v>
+    <row r="50" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="4">
-        <v>4010</v>
+        <v>2892</v>
       </c>
       <c r="F50" s="4">
-        <v>0.43580624150000002</v>
+        <v>-6.3168124389999996</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H50" s="5">
-        <v>3992.6</v>
+        <v>3087</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="59" t="s">
-        <v>40</v>
-      </c>
+      <c r="J50" s="59"/>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
@@ -4025,78 +3996,80 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B50, $C$2:$C$628, C50, $D$2:$D$628, D50, $E$2:$E$628, E50) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="42">
-        <v>46311.595833333333</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="O50"/>
+      <c r="P50"/>
+    </row>
+    <row r="51" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
+        <v>46286.375</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="5">
-        <v>20</v>
-      </c>
-      <c r="E51" s="5">
-        <v>271</v>
+      <c r="D51" s="4">
+        <v>5</v>
+      </c>
+      <c r="E51" s="4">
+        <v>702</v>
       </c>
       <c r="F51" s="4">
-        <v>0.64995357470000004</v>
+        <v>-6.7729083670000003</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="H51" s="5">
-        <v>269.25</v>
+        <v>753</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J51" s="58" t="s">
         <v>40</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="L51" s="17">
-        <f>20*283</f>
-        <v>5660</v>
+        <f>7470/2</f>
+        <v>3735</v>
       </c>
       <c r="M51" s="17">
         <f>ABS((D51*E51)-L51)</f>
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="N51" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B51, $C$2:$C$628, C51, $D$2:$D$628, D51, $E$2:$E$628, E51) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4">
-        <v>119</v>
+        <v>4456</v>
       </c>
       <c r="F52" s="4">
-        <v>0.79620531930000005</v>
+        <v>-8.206987475</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="H52" s="5">
-        <v>118.06</v>
+        <v>4854.3999999999996</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
@@ -4110,6 +4083,7 @@
         <v>Unique</v>
       </c>
       <c r="O52"/>
+      <c r="P52"/>
     </row>
     <row r="53" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="42">
@@ -4152,126 +4126,122 @@
       <c r="O53" s="71"/>
       <c r="P53" s="71"/>
     </row>
-    <row r="54" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="42">
-        <v>46301.393055555556</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="2" t="s">
+    <row r="54" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="5">
-        <v>1</v>
-      </c>
-      <c r="E54" s="5">
-        <v>19550</v>
+      <c r="D54" s="4">
+        <v>4</v>
+      </c>
+      <c r="E54" s="4">
+        <v>701</v>
       </c>
       <c r="F54" s="4">
-        <v>1.510981879</v>
+        <v>-8.4736910820000002</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="H54" s="5">
-        <v>19259</v>
+        <v>765.9</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="58" t="s">
+      <c r="J54" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="K54" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="L54" s="17">
-        <v>20020</v>
-      </c>
-      <c r="M54" s="17">
-        <f>ABS((D54*E54)-L54)</f>
-        <v>470</v>
-      </c>
-      <c r="N54" s="10" t="str">
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B54, $C$2:$C$628, C54, $D$2:$D$628, D54, $E$2:$E$628, E54) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3">
-        <v>46254.375</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="42">
+        <v>46314.375</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="4">
-        <v>7</v>
-      </c>
-      <c r="E55" s="4">
-        <v>2230</v>
+      <c r="D55" s="5">
+        <v>11</v>
+      </c>
+      <c r="E55" s="5">
+        <v>701</v>
       </c>
       <c r="F55" s="4">
-        <v>1.6362061889999999</v>
+        <v>-8.9610389609999999</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H55" s="5">
-        <v>2194.1</v>
+        <v>770</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="75" t="s">
-        <v>54</v>
-      </c>
-      <c r="K55" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="10" t="str">
+      <c r="J55" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="L55" s="17">
+        <v>8239</v>
+      </c>
+      <c r="M55" s="17">
+        <f>ABS((D55*E55)-L55)</f>
+        <v>528</v>
+      </c>
+      <c r="N55" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B55, $C$2:$C$628, C55, $D$2:$D$628, D55, $E$2:$E$628, E55) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O55"/>
-      <c r="P55"/>
-    </row>
-    <row r="56" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E56" s="4">
-        <v>836</v>
+        <v>4415</v>
       </c>
       <c r="F56" s="4">
-        <v>1.8270401949999999</v>
+        <v>-9.0515820700000003</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H56" s="5">
-        <v>821</v>
+        <v>4854.3999999999996</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="59" t="s">
-        <v>40</v>
-      </c>
+      <c r="J56" s="59"/>
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
@@ -4323,50 +4293,53 @@
       <c r="O57" s="71"/>
       <c r="P57" s="71"/>
     </row>
-    <row r="58" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="42">
+    <row r="58" spans="1:16" s="22" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="76">
         <v>46293.401388888888</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C58" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="78">
         <v>100</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="78">
         <v>329</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="51">
         <v>2.1739130430000002</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="H58" s="5">
+      <c r="H58" s="78">
         <v>322</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="17" t="s">
+      <c r="I58" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="K58" s="17" t="s">
+      <c r="K58" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="L58" s="17">
+      <c r="L58" s="40">
         <v>32400</v>
       </c>
-      <c r="M58" s="17">
+      <c r="M58" s="40">
         <f>ABS((D58*E58)-L58)</f>
         <v>500</v>
       </c>
-      <c r="N58" s="10" t="str">
+      <c r="N58" s="22" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B58, $C$2:$C$628, C58, $D$2:$D$628, D58, $E$2:$E$628, E58) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
+      </c>
+      <c r="P58" s="22" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4415,30 +4388,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="E60" s="4">
-        <v>1277</v>
+        <v>4164</v>
       </c>
       <c r="F60" s="4">
-        <v>3.2169414810000001</v>
+        <v>-9.1821155940000008</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H60" s="5">
-        <v>1237.2</v>
+        <v>4585</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
@@ -4495,35 +4468,35 @@
       <c r="O61" s="71"/>
       <c r="P61" s="71"/>
     </row>
-    <row r="62" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3">
-        <v>46252.6875</v>
+    <row r="62" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E62" s="4">
-        <v>122</v>
+        <v>2752</v>
       </c>
       <c r="F62" s="4">
-        <v>3.337286126</v>
+        <v>-10.85195983</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H62" s="5">
-        <v>118.06</v>
+        <v>3087</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="60" t="s">
+      <c r="J62" s="59" t="s">
         <v>40</v>
       </c>
       <c r="K62" s="16"/>
@@ -4533,46 +4506,54 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B62, $C$2:$C$628, C62, $D$2:$D$628, D62, $E$2:$E$628, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3">
-        <v>46252.635416666664</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="O62"/>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="42">
+        <v>46310.40347222222</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="4">
-        <v>50</v>
-      </c>
-      <c r="E63" s="4">
-        <v>850</v>
+      <c r="D63" s="5">
+        <v>300</v>
+      </c>
+      <c r="E63" s="5">
+        <v>32.01</v>
       </c>
       <c r="F63" s="4">
-        <v>3.5322777099999998</v>
+        <v>-11.009174310000001</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="H63" s="5">
-        <v>821</v>
+        <v>35.97</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="60" t="s">
+      <c r="J63" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" t="str">
+      <c r="K63" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="L63" s="17">
+        <v>10263</v>
+      </c>
+      <c r="M63" s="17">
+        <f>ABS((D63*E63)-L63)</f>
+        <v>660</v>
+      </c>
+      <c r="N63" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B63, $C$2:$C$628, C63, $D$2:$D$628, D63, $E$2:$E$628, E63) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P63"/>
     </row>
     <row r="64" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="42">
@@ -4620,7 +4601,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>46268.375</v>
       </c>
@@ -4802,38 +4783,47 @@
       <c r="O68" s="71"/>
       <c r="P68" s="71"/>
     </row>
-    <row r="69" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" s="1" t="s">
+    <row r="69" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="42">
+        <v>46314.375</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="4">
-        <v>3</v>
-      </c>
-      <c r="E69" s="4">
-        <v>3810</v>
+      <c r="D69" s="5">
+        <v>5</v>
+      </c>
+      <c r="E69" s="5">
+        <v>680</v>
       </c>
       <c r="F69" s="4">
-        <v>4.7854785480000004</v>
+        <v>-11.688311690000001</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="H69" s="5">
-        <v>3636</v>
+        <v>770</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="59"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+      <c r="J69" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="L69" s="17">
+        <v>3650</v>
+      </c>
+      <c r="M69" s="17">
+        <f>ABS((D69*E69)-L69)</f>
+        <v>250</v>
+      </c>
       <c r="N69" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B69, $C$2:$C$628, C69, $D$2:$D$628, D69, $E$2:$E$628, E69) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -4875,12 +4865,12 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="71" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
-        <v>46252.635416666664</v>
+        <v>46031.4375</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>10</v>
@@ -4889,32 +4879,35 @@
         <v>3</v>
       </c>
       <c r="E71" s="4">
-        <v>1302</v>
+        <v>1052</v>
       </c>
       <c r="F71" s="4">
-        <v>5.2376333659999998</v>
+        <v>-12.26753398</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="H71" s="5">
-        <v>1237.2</v>
+        <v>1199.0999999999999</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="59" t="s">
+      <c r="J71" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" t="str">
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17">
+        <f>ABS((D71*E71)-L71)</f>
+        <v>3156</v>
+      </c>
+      <c r="N71" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B71, $C$2:$C$628, C71, $D$2:$D$628, D71, $E$2:$E$628, E71) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O71"/>
-      <c r="P71"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="18"/>
     </row>
     <row r="72" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
@@ -5055,30 +5048,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="4">
-        <v>3830</v>
+        <v>4014</v>
       </c>
       <c r="F75" s="4">
-        <v>5.3355335530000003</v>
+        <v>-12.45365322</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="H75" s="5">
-        <v>3636</v>
+        <v>4585</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>8</v>
@@ -5091,6 +5084,8 @@
         <f>IF(COUNTIFS( $B$2:$B$628, B75, $C$2:$C$628, C75, $D$2:$D$628, D75, $E$2:$E$628, E75) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O75"/>
+      <c r="P75"/>
     </row>
     <row r="76" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="42">
@@ -5233,46 +5228,51 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="1" t="s">
+    <row r="79" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="42">
+        <v>46308.536805555559</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D79" s="4">
-        <v>50</v>
-      </c>
-      <c r="E79" s="4">
-        <v>206</v>
+      <c r="D79" s="5">
+        <v>200</v>
+      </c>
+      <c r="E79" s="5">
+        <v>31.1</v>
       </c>
       <c r="F79" s="4">
-        <v>5.6843833369999999</v>
+        <v>-13.53906033</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H79" s="5">
-        <v>194.92</v>
+        <v>35.97</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J79" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+      <c r="J79" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K79" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="L79" s="17">
+        <v>6580</v>
+      </c>
+      <c r="M79" s="17">
+        <f>ABS((D79*E79)-L79)</f>
+        <v>360</v>
+      </c>
       <c r="N79" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B79, $C$2:$C$628, C79, $D$2:$D$628, D79, $E$2:$E$628, E79) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O79"/>
-      <c r="P79"/>
     </row>
     <row r="80" spans="1:16" s="23" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="42">
@@ -5368,136 +5368,136 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="3">
-        <v>46261.375</v>
+    <row r="82" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E82" s="4">
-        <v>870</v>
+        <v>2660</v>
       </c>
       <c r="F82" s="4">
-        <v>5.9683313030000003</v>
+        <v>-13.83219955</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H82" s="5">
-        <v>821</v>
+        <v>3087</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J82" s="58" t="s">
+      <c r="J82" s="59"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="16"/>
+      <c r="M82" s="16"/>
+      <c r="N82" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$628, B82, $C$2:$C$628, C82, $D$2:$D$628, D82, $E$2:$E$628, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O82"/>
+      <c r="P82"/>
+    </row>
+    <row r="83" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="5">
+        <v>5</v>
+      </c>
+      <c r="E83" s="5">
+        <v>660</v>
+      </c>
+      <c r="F83" s="4">
+        <v>-14.28571429</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H83" s="5">
+        <v>770</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="K82" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="L82" s="17">
-        <v>17700</v>
-      </c>
-      <c r="M82" s="17">
-        <f>ABS((D82*E82)-L82)</f>
-        <v>300</v>
-      </c>
-      <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B82, $C$2:$C$628, C82, $D$2:$D$628, D82, $E$2:$E$628, E82) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P82" s="22"/>
-    </row>
-    <row r="83" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3">
-        <v>46283.375</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="4">
-        <v>20</v>
-      </c>
-      <c r="E83" s="4">
-        <v>870.2</v>
-      </c>
-      <c r="F83" s="4">
-        <v>5.9926918389999999</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H83" s="5">
-        <v>821</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="58" t="s">
-        <v>54</v>
-      </c>
       <c r="K83" s="17" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="L83" s="17">
-        <v>17920</v>
+        <v>3550</v>
       </c>
       <c r="M83" s="17">
         <f>ABS((D83*E83)-L83)</f>
-        <v>516</v>
+        <v>250</v>
       </c>
       <c r="N83" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B83, $C$2:$C$628, C83, $D$2:$D$628, D83, $E$2:$E$628, E83) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C84" s="1" t="s">
+    <row r="84" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="42">
+        <v>46308.538888888892</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D84" s="4">
-        <v>2</v>
-      </c>
-      <c r="E84" s="4">
-        <v>3856</v>
+      <c r="D84" s="5">
+        <v>8</v>
+      </c>
+      <c r="E84" s="5">
+        <v>2155</v>
       </c>
       <c r="F84" s="4">
-        <v>6.0506050609999997</v>
+        <v>-14.788453929999999</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H84" s="5">
-        <v>3636</v>
+        <v>2529</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J84" s="59"/>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
+      <c r="J84" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K84" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="L84" s="17">
+        <v>18040</v>
+      </c>
+      <c r="M84" s="17">
+        <f>ABS((D84*E84)-L84)</f>
+        <v>800</v>
+      </c>
       <c r="N84" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B84, $C$2:$C$628, C84, $D$2:$D$628, D84, $E$2:$E$628, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O84" s="18"/>
     </row>
     <row r="85" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="42">
@@ -5642,43 +5642,52 @@
       <c r="O87" s="10"/>
       <c r="P87" s="10"/>
     </row>
-    <row r="88" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C88" s="1" t="s">
+    <row r="88" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="42">
+        <v>46308.578472222223</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D88" s="4">
-        <v>5</v>
-      </c>
-      <c r="E88" s="4">
-        <v>3888</v>
+      <c r="D88" s="5">
+        <v>13</v>
+      </c>
+      <c r="E88" s="5">
+        <v>1209</v>
       </c>
       <c r="F88" s="4">
-        <v>6.9306930690000002</v>
+        <v>-15.11023733</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>49</v>
+        <v>314</v>
       </c>
       <c r="H88" s="5">
-        <v>3636</v>
+        <v>1424.2</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J88" s="59"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="16"/>
+      <c r="J88" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K88" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="L88" s="17">
+        <v>17017</v>
+      </c>
+      <c r="M88" s="17">
+        <f>ABS((D88*E88)-L88)</f>
+        <v>1300</v>
+      </c>
       <c r="N88" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B88, $C$2:$C$628, C88, $D$2:$D$628, D88, $E$2:$E$628, E88) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O88" s="23"/>
+      <c r="O88" s="10"/>
       <c r="P88" s="10"/>
     </row>
     <row r="89" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5764,7 +5773,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>46267.375</v>
       </c>
@@ -5905,46 +5914,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="3">
-        <v>46252.645138888889</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C94" s="1" t="s">
+    <row r="94" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="42">
+        <v>46304.387499999997</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D94" s="4">
-        <v>10</v>
-      </c>
-      <c r="E94" s="4">
-        <v>401</v>
+      <c r="D94" s="5">
+        <v>500</v>
+      </c>
+      <c r="E94" s="5">
+        <v>30.3</v>
       </c>
       <c r="F94" s="4">
-        <v>8.0280172410000006</v>
+        <v>-15.763135950000001</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H94" s="5">
-        <v>371.2</v>
+        <v>35.97</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="16"/>
+      <c r="J94" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K94" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="L94" s="17">
+        <v>15850</v>
+      </c>
+      <c r="M94" s="17">
+        <f>ABS((D94*E94)-L94)</f>
+        <v>700</v>
+      </c>
       <c r="N94" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B94, $C$2:$C$628, C94, $D$2:$D$628, D94, $E$2:$E$628, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="42">
         <v>46293.375694444447</v>
       </c>
@@ -6320,46 +6336,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" s="1" t="s">
+    <row r="103" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="42">
+        <v>46304.388888888891</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="4">
-        <v>50</v>
-      </c>
-      <c r="E103" s="4">
-        <v>212</v>
+      <c r="D103" s="5">
+        <v>9</v>
+      </c>
+      <c r="E103" s="5">
+        <v>2105</v>
       </c>
       <c r="F103" s="4">
-        <v>8.7625692589999993</v>
+        <v>-16.76551997</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H103" s="5">
-        <v>194.92</v>
+        <v>2529</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J103" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="K103" s="16"/>
-      <c r="L103" s="16"/>
-      <c r="M103" s="16"/>
+      <c r="J103" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="L103" s="17">
+        <v>19395</v>
+      </c>
+      <c r="M103" s="17">
+        <f>ABS((D103*E103)-L103)</f>
+        <v>450</v>
+      </c>
       <c r="N103" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B103, $C$2:$C$628, C103, $D$2:$D$628, D103, $E$2:$E$628, E103) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6550,7 +6573,7 @@
       <c r="O107" s="27"/>
       <c r="P107" s="27"/>
     </row>
-    <row r="108" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6694,7 +6717,7 @@
       <c r="O110" s="10"/>
       <c r="P110" s="10"/>
     </row>
-    <row r="111" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="42">
         <v>46316.559907407405</v>
       </c>
@@ -6702,7 +6725,7 @@
         <v>9</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D111" s="5">
         <v>50</v>
@@ -6825,46 +6848,46 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="3">
-        <v>46268.385416666664</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C114" s="1" t="s">
+    <row r="114" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D114" s="4">
-        <v>100</v>
-      </c>
-      <c r="E114" s="4">
-        <v>214</v>
+      <c r="D114" s="5">
+        <v>5</v>
+      </c>
+      <c r="E114" s="5">
+        <v>640</v>
       </c>
       <c r="F114" s="4">
-        <v>9.7886312330000003</v>
+        <v>-16.883116879999999</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H114" s="5">
-        <v>194.92</v>
+        <v>770</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J114" s="58" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K114" s="17" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="L114" s="17">
-        <v>21900</v>
+        <v>3450</v>
       </c>
       <c r="M114" s="17">
         <f>ABS((D114*E114)-L114)</f>
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="N114" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B114, $C$2:$C$628, C114, $D$2:$D$628, D114, $E$2:$E$628, E114) &gt; 1, "Duplicate", "Unique")</f>
@@ -7279,7 +7302,7 @@
       </c>
       <c r="O123" s="27"/>
     </row>
-    <row r="124" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="11">
         <v>46243.375</v>
       </c>
@@ -7328,7 +7351,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="38">
         <v>46273.375</v>
       </c>
@@ -7378,7 +7401,7 @@
       </c>
       <c r="P125" s="27"/>
     </row>
-    <row r="126" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="28">
         <v>46274.375</v>
       </c>
@@ -7428,7 +7451,7 @@
       </c>
       <c r="P126" s="27"/>
     </row>
-    <row r="127" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>46281.375</v>
       </c>
@@ -7720,7 +7743,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="134" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="42">
         <v>46296.443055555559</v>
       </c>
@@ -8087,7 +8110,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8357,7 +8380,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="42">
         <v>46289.390277777777</v>
       </c>
@@ -8406,51 +8429,46 @@
         <v>236</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="3">
-        <v>46275.457638888889</v>
+    <row r="149" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D149" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E149" s="4">
-        <v>222</v>
+        <v>2560</v>
       </c>
       <c r="F149" s="4">
-        <v>13.892879130000001</v>
+        <v>-17.071590539999999</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H149" s="5">
-        <v>194.92</v>
+        <v>3087</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J149" s="58" t="s">
+      <c r="J149" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="K149" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="L149" s="17">
-        <v>56375</v>
-      </c>
-      <c r="M149" s="17">
-        <f>ABS((D149*E149)-L149)</f>
-        <v>34175</v>
-      </c>
-      <c r="N149" s="10" t="str">
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
+      <c r="M149" s="16"/>
+      <c r="N149" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B149, $C$2:$C$628, C149, $D$2:$D$628, D149, $E$2:$E$628, E149) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O149"/>
+      <c r="P149"/>
     </row>
     <row r="150" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="8" t="s">
@@ -8650,7 +8668,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -9005,7 +9023,7 @@
       </c>
       <c r="O162" s="27"/>
     </row>
-    <row r="163" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -9182,7 +9200,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>61</v>
       </c>
@@ -9527,7 +9545,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9612,7 +9630,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="28">
         <v>46267.425694444442</v>
       </c>
@@ -9662,7 +9680,7 @@
       </c>
       <c r="P177" s="27"/>
     </row>
-    <row r="178" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="28">
         <v>46280.593055555553</v>
       </c>
@@ -9936,51 +9954,46 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="3">
-        <v>46261.375</v>
+    <row r="185" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D185" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E185" s="4">
-        <v>204</v>
+        <v>660</v>
       </c>
       <c r="F185" s="4">
-        <v>17.477685000000001</v>
+        <v>-20.625375829999999</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="H185" s="5">
-        <v>173.65</v>
+        <v>831.5</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J185" s="58" t="s">
+      <c r="J185" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="K185" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="L185" s="17">
-        <v>10550</v>
-      </c>
-      <c r="M185" s="17">
-        <f>ABS((D185*E185)-L185)</f>
-        <v>350</v>
-      </c>
-      <c r="N185" s="10" t="str">
+      <c r="K185" s="16"/>
+      <c r="L185" s="16"/>
+      <c r="M185" s="16"/>
+      <c r="N185" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B185, $C$2:$C$628, C185, $D$2:$D$628, D185, $E$2:$E$628, E185) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O185"/>
+      <c r="P185"/>
     </row>
     <row r="186" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
@@ -10161,7 +10174,7 @@
       </c>
       <c r="O189"/>
     </row>
-    <row r="190" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
         <v>46274.375</v>
       </c>
@@ -10614,7 +10627,7 @@
       <c r="O200" s="10"/>
       <c r="P200" s="10"/>
     </row>
-    <row r="201" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="28">
         <v>46281.443055555559</v>
       </c>
@@ -10663,7 +10676,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="28">
         <v>46281.388888888891</v>
       </c>
@@ -10798,48 +10811,55 @@
       </c>
       <c r="P204" s="27"/>
     </row>
-    <row r="205" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="6" t="s">
-        <v>61</v>
+    <row r="205" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D205" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E205" s="4">
-        <v>2435</v>
+        <v>726</v>
       </c>
       <c r="F205" s="4">
-        <v>20.09864365</v>
+        <v>-29.855072459999999</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="H205" s="5">
-        <v>2027.5</v>
+        <v>1035</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J205" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="K205" s="16"/>
-      <c r="L205" s="16"/>
-      <c r="M205" s="16"/>
-      <c r="N205" t="str">
+      <c r="J205" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K205" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L205" s="17">
+        <v>17940</v>
+      </c>
+      <c r="M205" s="17">
+        <f>ABS((D205*E205)-L205)</f>
+        <v>10680</v>
+      </c>
+      <c r="N205" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B205, $C$2:$C$628, C205, $D$2:$D$628, D205, $E$2:$E$628, E205) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O205" s="10"/>
       <c r="P205" s="10"/>
     </row>
-    <row r="206" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -11206,7 +11226,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="214" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="28">
         <v>46265.375694444447</v>
       </c>
@@ -11255,7 +11275,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="38">
         <v>46243.505555555559</v>
       </c>
@@ -11304,7 +11324,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="28">
         <v>46280.588194444441</v>
       </c>
@@ -11734,45 +11754,51 @@
       <c r="O225" s="27"/>
       <c r="P225" s="27"/>
     </row>
-    <row r="226" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="6" t="s">
-        <v>61</v>
+    <row r="226" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D226" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E226" s="4">
-        <v>2470</v>
+        <v>706</v>
       </c>
       <c r="F226" s="4">
-        <v>21.82490752</v>
+        <v>-31.78743961</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="H226" s="5">
-        <v>2027.5</v>
+        <v>1035</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J226" s="59" t="s">
+      <c r="J226" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="K226" s="16"/>
-      <c r="L226" s="16"/>
-      <c r="M226" s="16"/>
-      <c r="N226" t="str">
+      <c r="K226" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L226" s="17">
+        <v>17940</v>
+      </c>
+      <c r="M226" s="17">
+        <f>ABS((D226*E226)-L226)</f>
+        <v>10880</v>
+      </c>
+      <c r="N226" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$628, B226, $C$2:$C$628, C226, $D$2:$D$628, D226, $E$2:$E$628, E226) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P226" s="22"/>
     </row>
     <row r="227" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="11">
@@ -11806,7 +11832,7 @@
         <v>116</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B227, $C$2:$C$628, C227, $D$2:$D$628, D227, $E$2:$E$628, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="0">IF(COUNTIFS( $B$2:$B$628, B227, $C$2:$C$628, C227, $D$2:$D$628, D227, $E$2:$E$628, E227) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -11852,7 +11878,7 @@
         <v>527.5</v>
       </c>
       <c r="N228" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B228, $C$2:$C$628, C228, $D$2:$D$628, D228, $E$2:$E$628, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="27"/>
@@ -11895,7 +11921,7 @@
       <c r="L229" s="25"/>
       <c r="M229" s="25"/>
       <c r="N229" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B229, $C$2:$C$628, C229, $D$2:$D$628, D229, $E$2:$E$628, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="27"/>
@@ -11943,7 +11969,7 @@
         <v>260</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B230, $C$2:$C$628, C230, $D$2:$D$628, D230, $E$2:$E$628, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11989,7 +12015,7 @@
         <v>1000</v>
       </c>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B231, $C$2:$C$628, C231, $D$2:$D$628, D231, $E$2:$E$628, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12023,7 +12049,7 @@
       </c>
       <c r="J232" s="32"/>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B232, $C$2:$C$628, C232, $D$2:$D$628, D232, $E$2:$E$628, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12069,7 +12095,7 @@
         <v>300</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B233, $C$2:$C$628, C233, $D$2:$D$628, D233, $E$2:$E$628, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12105,7 +12131,7 @@
         <v>116</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B234, $C$2:$C$628, C234, $D$2:$D$628, D234, $E$2:$E$628, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12147,11 +12173,11 @@
         <v>10400</v>
       </c>
       <c r="M235" s="17">
-        <f>ABS((D235*E235)-L235)</f>
+        <f t="shared" ref="M235:M244" si="1">ABS((D235*E235)-L235)</f>
         <v>300</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B235, $C$2:$C$628, C235, $D$2:$D$628, D235, $E$2:$E$628, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12193,11 +12219,11 @@
         <v>12800</v>
       </c>
       <c r="M236" s="17">
-        <f>ABS((D236*E236)-L236)</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="N236" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B236, $C$2:$C$628, C236, $D$2:$D$628, D236, $E$2:$E$628, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12239,11 +12265,11 @@
         <v>5905</v>
       </c>
       <c r="M237" s="17">
-        <f>ABS((D237*E237)-L237)</f>
+        <f t="shared" si="1"/>
         <v>275</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B237, $C$2:$C$628, C237, $D$2:$D$628, D237, $E$2:$E$628, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12285,11 +12311,11 @@
         <v>4680</v>
       </c>
       <c r="M238" s="25">
-        <f>ABS((D238*E238)-L238)</f>
+        <f t="shared" si="1"/>
         <v>140</v>
       </c>
       <c r="N238" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B238, $C$2:$C$628, C238, $D$2:$D$628, D238, $E$2:$E$628, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="P238" s="27"/>
@@ -12332,11 +12358,11 @@
         <v>4520</v>
       </c>
       <c r="M239" s="25">
-        <f>ABS((D239*E239)-L239)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N239" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B239, $C$2:$C$628, C239, $D$2:$D$628, D239, $E$2:$E$628, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12378,11 +12404,11 @@
         <v>18960</v>
       </c>
       <c r="M240" s="17">
-        <f>ABS((D240*E240)-L240)</f>
+        <f t="shared" si="1"/>
         <v>816</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B240, $C$2:$C$628, C240, $D$2:$D$628, D240, $E$2:$E$628, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12424,11 +12450,11 @@
         <v>4264</v>
       </c>
       <c r="M241" s="25">
-        <f>ABS((D241*E241)-L241)</f>
+        <f t="shared" si="1"/>
         <v>320</v>
       </c>
       <c r="N241" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B241, $C$2:$C$628, C241, $D$2:$D$628, D241, $E$2:$E$628, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="27"/>
@@ -12472,11 +12498,11 @@
         <v>5282</v>
       </c>
       <c r="M242" s="25">
-        <f>ABS((D242*E242)-L242)</f>
+        <f t="shared" si="1"/>
         <v>448</v>
       </c>
       <c r="N242" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B242, $C$2:$C$628, C242, $D$2:$D$628, D242, $E$2:$E$628, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="27"/>
@@ -12520,15 +12546,15 @@
         <v>2640</v>
       </c>
       <c r="M243" s="17">
-        <f>ABS((D243*E243)-L243)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B243, $C$2:$C$628, C243, $D$2:$D$628, D243, $E$2:$E$628, E243) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -12566,11 +12592,11 @@
         <v>8049</v>
       </c>
       <c r="M244" s="17">
-        <f>ABS((D244*E244)-L244)</f>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B244, $C$2:$C$628, C244, $D$2:$D$628, D244, $E$2:$E$628, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="36" t="s">
@@ -12610,7 +12636,7 @@
         <v>117</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B245, $C$2:$C$628, C245, $D$2:$D$628, D245, $E$2:$E$628, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12649,7 +12675,7 @@
       <c r="L246" s="17"/>
       <c r="M246" s="17"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B246, $C$2:$C$628, C246, $D$2:$D$628, D246, $E$2:$E$628, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="10"/>
@@ -12697,7 +12723,7 @@
         <v>500</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B247, $C$2:$C$628, C247, $D$2:$D$628, D247, $E$2:$E$628, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12743,7 +12769,7 @@
         <v>150</v>
       </c>
       <c r="N248" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B248, $C$2:$C$628, C248, $D$2:$D$628, D248, $E$2:$E$628, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12789,7 +12815,7 @@
         <v>250</v>
       </c>
       <c r="N249" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B249, $C$2:$C$628, C249, $D$2:$D$628, D249, $E$2:$E$628, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12835,7 +12861,7 @@
         <v>370</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B250, $C$2:$C$628, C250, $D$2:$D$628, D250, $E$2:$E$628, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P250" s="27"/>
@@ -12870,7 +12896,7 @@
       </c>
       <c r="J251" s="32"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B251, $C$2:$C$628, C251, $D$2:$D$628, D251, $E$2:$E$628, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P251" s="27"/>
@@ -12905,7 +12931,7 @@
       </c>
       <c r="J252" s="32"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B252, $C$2:$C$628, C252, $D$2:$D$628, D252, $E$2:$E$628, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12951,11 +12977,11 @@
         <v>290</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B253, $C$2:$C$628, C253, $D$2:$D$628, D253, $E$2:$E$628, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -12997,7 +13023,7 @@
         <v>48320</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B254, $C$2:$C$628, C254, $D$2:$D$628, D254, $E$2:$E$628, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="36" t="s">
@@ -13046,7 +13072,7 @@
         <v>500</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B255, $C$2:$C$628, C255, $D$2:$D$628, D255, $E$2:$E$628, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13092,7 +13118,7 @@
         <v>280</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B256, $C$2:$C$628, C256, $D$2:$D$628, D256, $E$2:$E$628, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13126,7 +13152,7 @@
       </c>
       <c r="J257" s="32"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B257, $C$2:$C$628, C257, $D$2:$D$628, D257, $E$2:$E$628, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13162,7 +13188,7 @@
         <v>117</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B258, $C$2:$C$628, C258, $D$2:$D$628, D258, $E$2:$E$628, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N323" si="2">IF(COUNTIFS( $B$2:$B$628, B258, $C$2:$C$628, C258, $D$2:$D$628, D258, $E$2:$E$628, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13201,7 +13227,7 @@
         <v>144</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B259, $C$2:$C$628, C259, $D$2:$D$628, D259, $E$2:$E$628, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13237,7 +13263,7 @@
         <v>116</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B260, $C$2:$C$628, C260, $D$2:$D$628, D260, $E$2:$E$628, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13271,7 +13297,7 @@
       </c>
       <c r="J261" s="32"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B261, $C$2:$C$628, C261, $D$2:$D$628, D261, $E$2:$E$628, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13317,12 +13343,12 @@
         <v>250</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B262, $C$2:$C$628, C262, $D$2:$D$628, D262, $E$2:$E$628, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P262" s="27"/>
     </row>
-    <row r="263" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3">
         <v>46266.375</v>
       </c>
@@ -13364,7 +13390,7 @@
         <v>300</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B263, $C$2:$C$628, C263, $D$2:$D$628, D263, $E$2:$E$628, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="36" t="s">
@@ -13414,7 +13440,7 @@
         <v>300</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B264, $C$2:$C$628, C264, $D$2:$D$628, D264, $E$2:$E$628, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13460,7 +13486,7 @@
         <v>300</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B265, $C$2:$C$628, C265, $D$2:$D$628, D265, $E$2:$E$628, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13494,7 +13520,7 @@
       </c>
       <c r="J266" s="32"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B266, $C$2:$C$628, C266, $D$2:$D$628, D266, $E$2:$E$628, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P266" s="27"/>
@@ -13541,11 +13567,11 @@
         <v>500</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B267, $C$2:$C$628, C267, $D$2:$D$628, D267, $E$2:$E$628, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -13587,7 +13613,7 @@
         <v>47900</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B268, $C$2:$C$628, C268, $D$2:$D$628, D268, $E$2:$E$628, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="36" t="s">
@@ -13636,11 +13662,11 @@
         <v>420</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B269, $C$2:$C$628, C269, $D$2:$D$628, D269, $E$2:$E$628, E269) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3">
         <v>46266.375</v>
       </c>
@@ -13682,14 +13708,14 @@
         <v>650</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B270, $C$2:$C$628, C270, $D$2:$D$628, D270, $E$2:$E$628, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="36" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="271" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -13731,7 +13757,7 @@
         <v>495</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B271, $C$2:$C$628, C271, $D$2:$D$628, D271, $E$2:$E$628, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="36" t="s">
@@ -13768,7 +13794,7 @@
       </c>
       <c r="J272" s="32"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B272, $C$2:$C$628, C272, $D$2:$D$628, D272, $E$2:$E$628, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O272" s="27"/>
@@ -13808,12 +13834,12 @@
       <c r="L273" s="16"/>
       <c r="M273" s="16"/>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B273, $C$2:$C$628, C273, $D$2:$D$628, D273, $E$2:$E$628, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O273"/>
     </row>
-    <row r="274" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13855,7 +13881,7 @@
         <v>300</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B274, $C$2:$C$628, C274, $D$2:$D$628, D274, $E$2:$E$628, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="36" t="s">
@@ -13895,7 +13921,7 @@
         <v>117</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B275, $C$2:$C$628, C275, $D$2:$D$628, D275, $E$2:$E$628, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13941,7 +13967,7 @@
         <v>650</v>
       </c>
       <c r="N276" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B276, $C$2:$C$628, C276, $D$2:$D$628, D276, $E$2:$E$628, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O276"/>
@@ -13989,7 +14015,7 @@
         <v>450</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B277, $C$2:$C$628, C277, $D$2:$D$628, D277, $E$2:$E$628, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14025,7 +14051,7 @@
         <v>116</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B278, $C$2:$C$628, C278, $D$2:$D$628, D278, $E$2:$E$628, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14071,7 +14097,7 @@
         <v>1800</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B279, $C$2:$C$628, C279, $D$2:$D$628, D279, $E$2:$E$628, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14117,7 +14143,7 @@
         <v>47480</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B280, $C$2:$C$628, C280, $D$2:$D$628, D280, $E$2:$E$628, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14153,7 +14179,7 @@
         <v>116</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B281, $C$2:$C$628, C281, $D$2:$D$628, D281, $E$2:$E$628, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14199,7 +14225,7 @@
         <v>300</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B282, $C$2:$C$628, C282, $D$2:$D$628, D282, $E$2:$E$628, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14245,7 +14271,7 @@
         <v>340</v>
       </c>
       <c r="N283" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B283, $C$2:$C$628, C283, $D$2:$D$628, D283, $E$2:$E$628, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14281,7 +14307,7 @@
         <v>116</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B284, $C$2:$C$628, C284, $D$2:$D$628, D284, $E$2:$E$628, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14327,7 +14353,7 @@
         <v>300</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B285, $C$2:$C$628, C285, $D$2:$D$628, D285, $E$2:$E$628, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14373,7 +14399,7 @@
         <v>480</v>
       </c>
       <c r="N286" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B286, $C$2:$C$628, C286, $D$2:$D$628, D286, $E$2:$E$628, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14407,7 +14433,7 @@
       </c>
       <c r="J287" s="32"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B287, $C$2:$C$628, C287, $D$2:$D$628, D287, $E$2:$E$628, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14453,7 +14479,7 @@
         <v>300</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B288, $C$2:$C$628, C288, $D$2:$D$628, D288, $E$2:$E$628, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14494,7 +14520,7 @@
       <c r="L289" s="16"/>
       <c r="M289" s="16"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B289, $C$2:$C$628, C289, $D$2:$D$628, D289, $E$2:$E$628, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14540,7 +14566,7 @@
         <v>250</v>
       </c>
       <c r="N290" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B290, $C$2:$C$628, C290, $D$2:$D$628, D290, $E$2:$E$628, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14576,7 +14602,7 @@
         <v>116</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B291, $C$2:$C$628, C291, $D$2:$D$628, D291, $E$2:$E$628, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14612,7 +14638,7 @@
         <v>116</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B292, $C$2:$C$628, C292, $D$2:$D$628, D292, $E$2:$E$628, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14648,7 +14674,7 @@
         <v>117</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B293, $C$2:$C$628, C293, $D$2:$D$628, D293, $E$2:$E$628, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14682,7 +14708,7 @@
       </c>
       <c r="J294" s="32"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B294, $C$2:$C$628, C294, $D$2:$D$628, D294, $E$2:$E$628, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14718,7 +14744,7 @@
         <v>116</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B295, $C$2:$C$628, C295, $D$2:$D$628, D295, $E$2:$E$628, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14754,7 +14780,7 @@
         <v>116</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B296, $C$2:$C$628, C296, $D$2:$D$628, D296, $E$2:$E$628, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14800,7 +14826,7 @@
         <v>450</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B297, $C$2:$C$628, C297, $D$2:$D$628, D297, $E$2:$E$628, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14834,7 +14860,7 @@
       </c>
       <c r="J298" s="32"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B298, $C$2:$C$628, C298, $D$2:$D$628, D298, $E$2:$E$628, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14868,7 +14894,7 @@
       </c>
       <c r="J299" s="32"/>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B299, $C$2:$C$628, C299, $D$2:$D$628, D299, $E$2:$E$628, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14904,7 +14930,7 @@
         <v>152</v>
       </c>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B300, $C$2:$C$628, C300, $D$2:$D$628, D300, $E$2:$E$628, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14950,7 +14976,7 @@
         <v>285</v>
       </c>
       <c r="N301" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B301, $C$2:$C$628, C301, $D$2:$D$628, D301, $E$2:$E$628, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14996,7 +15022,7 @@
         <v>726</v>
       </c>
       <c r="N302" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B302, $C$2:$C$628, C302, $D$2:$D$628, D302, $E$2:$E$628, E302) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15030,7 +15056,7 @@
       </c>
       <c r="J303" s="32"/>
       <c r="N303" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B303, $C$2:$C$628, C303, $D$2:$D$628, D303, $E$2:$E$628, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15066,7 +15092,7 @@
         <v>117</v>
       </c>
       <c r="N304" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B304, $C$2:$C$628, C304, $D$2:$D$628, D304, $E$2:$E$628, E304) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15102,7 +15128,7 @@
         <v>117</v>
       </c>
       <c r="N305" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B305, $C$2:$C$628, C305, $D$2:$D$628, D305, $E$2:$E$628, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15138,7 +15164,7 @@
         <v>116</v>
       </c>
       <c r="N306" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B306, $C$2:$C$628, C306, $D$2:$D$628, D306, $E$2:$E$628, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15172,7 +15198,7 @@
       </c>
       <c r="J307" s="32"/>
       <c r="N307" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B307, $C$2:$C$628, C307, $D$2:$D$628, D307, $E$2:$E$628, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O307" s="27"/>
@@ -15219,7 +15245,7 @@
         <v>275</v>
       </c>
       <c r="N308" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B308, $C$2:$C$628, C308, $D$2:$D$628, D308, $E$2:$E$628, E308) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15253,7 +15279,7 @@
       </c>
       <c r="J309" s="32"/>
       <c r="N309" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B309, $C$2:$C$628, C309, $D$2:$D$628, D309, $E$2:$E$628, E309) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15299,7 +15325,7 @@
         <v>250</v>
       </c>
       <c r="N310" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B310, $C$2:$C$628, C310, $D$2:$D$628, D310, $E$2:$E$628, E310) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P310" s="27"/>
@@ -15346,7 +15372,7 @@
         <v>250</v>
       </c>
       <c r="N311" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B311, $C$2:$C$628, C311, $D$2:$D$628, D311, $E$2:$E$628, E311) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15382,7 +15408,7 @@
         <v>54</v>
       </c>
       <c r="N312" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B312, $C$2:$C$628, C312, $D$2:$D$628, D312, $E$2:$E$628, E312) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15416,7 +15442,7 @@
       </c>
       <c r="J313" s="32"/>
       <c r="N313" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B313, $C$2:$C$628, C313, $D$2:$D$628, D313, $E$2:$E$628, E313) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15450,7 +15476,7 @@
       </c>
       <c r="J314" s="32"/>
       <c r="N314" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B314, $C$2:$C$628, C314, $D$2:$D$628, D314, $E$2:$E$628, E314) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15496,7 +15522,7 @@
         <v>300</v>
       </c>
       <c r="N315" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B315, $C$2:$C$628, C315, $D$2:$D$628, D315, $E$2:$E$628, E315) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15542,7 +15568,7 @@
         <v>235</v>
       </c>
       <c r="N316" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B316, $C$2:$C$628, C316, $D$2:$D$628, D316, $E$2:$E$628, E316) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15576,7 +15602,7 @@
       </c>
       <c r="J317" s="32"/>
       <c r="N317" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B317, $C$2:$C$628, C317, $D$2:$D$628, D317, $E$2:$E$628, E317) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15612,7 +15638,7 @@
         <v>117</v>
       </c>
       <c r="N318" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B318, $C$2:$C$628, C318, $D$2:$D$628, D318, $E$2:$E$628, E318) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15648,7 +15674,7 @@
         <v>117</v>
       </c>
       <c r="N319" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B319, $C$2:$C$628, C319, $D$2:$D$628, D319, $E$2:$E$628, E319) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15687,7 +15713,7 @@
       <c r="L320" s="25"/>
       <c r="M320" s="25"/>
       <c r="N320" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B320, $C$2:$C$628, C320, $D$2:$D$628, D320, $E$2:$E$628, E320) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O320" s="27"/>
@@ -15728,7 +15754,7 @@
       <c r="L321" s="25"/>
       <c r="M321" s="25"/>
       <c r="N321" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B321, $C$2:$C$628, C321, $D$2:$D$628, D321, $E$2:$E$628, E321) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O321" s="27"/>
@@ -15776,7 +15802,7 @@
         <v>250</v>
       </c>
       <c r="N322" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B322, $C$2:$C$628, C322, $D$2:$D$628, D322, $E$2:$E$628, E322) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15812,7 +15838,7 @@
         <v>116</v>
       </c>
       <c r="N323" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B323, $C$2:$C$628, C323, $D$2:$D$628, D323, $E$2:$E$628, E323) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23066,19 +23092,6 @@
       <c r="I982" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P323">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState ref="A2:P323">
-      <sortCondition ref="F1"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -23667,7 +23680,7 @@
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B2, $C$2:$C$628, C2, $D$2:$D$628, D2, $E$2:$E$628, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$628, B2, $C$2:$C$628, C2, $D$2:$D$628, D2, $E$2:$E$628, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -23708,7 +23721,7 @@
       <c r="L3" s="16"/>
       <c r="M3" s="16"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B3, $C$2:$C$628, C3, $D$2:$D$628, D3, $E$2:$E$628, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -23756,7 +23769,7 @@
         <v>34175</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B4, $C$2:$C$628, C4, $D$2:$D$628, D4, $E$2:$E$628, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -23804,7 +23817,7 @@
         <v>350</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B5, $C$2:$C$628, C5, $D$2:$D$628, D5, $E$2:$E$628, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -23852,7 +23865,7 @@
         <v>500</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B6, $C$2:$C$628, C6, $D$2:$D$628, D6, $E$2:$E$628, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -23893,7 +23906,7 @@
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B7, $C$2:$C$628, C7, $D$2:$D$628, D7, $E$2:$E$628, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -23934,7 +23947,7 @@
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B8, $C$2:$C$628, C8, $D$2:$D$628, D8, $E$2:$E$628, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -23973,7 +23986,7 @@
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B9, $C$2:$C$628, C9, $D$2:$D$628, D9, $E$2:$E$628, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="23"/>
@@ -24012,7 +24025,7 @@
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B10, $C$2:$C$628, C10, $D$2:$D$628, D10, $E$2:$E$628, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="18"/>
@@ -24051,7 +24064,7 @@
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B11, $C$2:$C$628, C11, $D$2:$D$628, D11, $E$2:$E$628, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -24092,7 +24105,7 @@
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B12, $C$2:$C$628, C12, $D$2:$D$628, D12, $E$2:$E$628, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24129,7 +24142,7 @@
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B13, $C$2:$C$628, C13, $D$2:$D$628, D13, $E$2:$E$628, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24168,7 +24181,7 @@
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B14, $C$2:$C$628, C14, $D$2:$D$628, D14, $E$2:$E$628, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14"/>
@@ -24209,7 +24222,7 @@
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B15, $C$2:$C$628, C15, $D$2:$D$628, D15, $E$2:$E$628, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24255,7 +24268,7 @@
         <v>516</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B16, $C$2:$C$628, C16, $D$2:$D$628, D16, $E$2:$E$628, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24301,7 +24314,7 @@
         <v>300</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B17, $C$2:$C$628, C17, $D$2:$D$628, D17, $E$2:$E$628, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P17" s="22"/>
@@ -24343,7 +24356,7 @@
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B18, $C$2:$C$628, C18, $D$2:$D$628, D18, $E$2:$E$628, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18"/>
@@ -24382,7 +24395,7 @@
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B19, $C$2:$C$628, C19, $D$2:$D$628, D19, $E$2:$E$628, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -24423,7 +24436,7 @@
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B20, $C$2:$C$628, C20, $D$2:$D$628, D20, $E$2:$E$628, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P20"/>
@@ -24461,7 +24474,7 @@
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B21, $C$2:$C$628, C21, $D$2:$D$628, D21, $E$2:$E$628, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -24501,7 +24514,7 @@
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B22, $C$2:$C$628, C22, $D$2:$D$628, D22, $E$2:$E$628, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -24549,7 +24562,7 @@
         <v>470</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B23, $C$2:$C$628, C23, $D$2:$D$628, D23, $E$2:$E$628, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="10"/>
@@ -24590,7 +24603,7 @@
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B24, $C$2:$C$628, C24, $D$2:$D$628, D24, $E$2:$E$628, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24636,7 +24649,7 @@
         <v>689.99999999999636</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B25, $C$2:$C$628, C25, $D$2:$D$628, D25, $E$2:$E$628, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="10"/>
@@ -24685,7 +24698,7 @@
         <v>135</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B26, $C$2:$C$628, C26, $D$2:$D$628, D26, $E$2:$E$628, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="10"/>
@@ -24734,7 +24747,7 @@
         <v>240</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B27, $C$2:$C$628, C27, $D$2:$D$628, D27, $E$2:$E$628, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
@@ -24775,7 +24788,7 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B28, $C$2:$C$628, C28, $D$2:$D$628, D28, $E$2:$E$628, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -24816,7 +24829,7 @@
       <c r="L29" s="69"/>
       <c r="M29" s="69"/>
       <c r="N29" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B29, $C$2:$C$628, C29, $D$2:$D$628, D29, $E$2:$E$628, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="71"/>
@@ -24857,7 +24870,7 @@
       <c r="L30" s="70"/>
       <c r="M30" s="69"/>
       <c r="N30" s="71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B30, $C$2:$C$628, C30, $D$2:$D$628, D30, $E$2:$E$628, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24896,7 +24909,7 @@
       <c r="L31" s="69"/>
       <c r="M31" s="69"/>
       <c r="N31" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B31, $C$2:$C$628, C31, $D$2:$D$628, D31, $E$2:$E$628, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="71"/>
@@ -24937,7 +24950,7 @@
       <c r="L32" s="69"/>
       <c r="M32" s="69"/>
       <c r="N32" s="70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B32, $C$2:$C$628, C32, $D$2:$D$628, D32, $E$2:$E$628, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24974,7 +24987,7 @@
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B33, $C$2:$C$628, C33, $D$2:$D$628, D33, $E$2:$E$628, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -25023,7 +25036,7 @@
         <v>440</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B34, $C$2:$C$628, C34, $D$2:$D$628, D34, $E$2:$E$628, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25060,7 +25073,7 @@
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B35, $C$2:$C$628, C35, $D$2:$D$628, D35, $E$2:$E$628, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -25108,7 +25121,7 @@
         <v>253</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B36, $C$2:$C$628, C36, $D$2:$D$628, D36, $E$2:$E$628, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25147,7 +25160,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B37, $C$2:$C$628, C37, $D$2:$D$628, D37, $E$2:$E$628, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -25186,7 +25199,7 @@
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B38, $C$2:$C$628, C38, $D$2:$D$628, D38, $E$2:$E$628, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -25231,11 +25244,11 @@
         <v>3865</v>
       </c>
       <c r="M39" s="17">
-        <f t="shared" ref="M39:M44" si="0">ABS((D39*E39)-L39)</f>
+        <f t="shared" ref="M39:M44" si="1">ABS((D39*E39)-L39)</f>
         <v>235</v>
       </c>
       <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B39, $C$2:$C$628, C39, $D$2:$D$628, D39, $E$2:$E$628, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25278,11 +25291,11 @@
         <v>2830</v>
       </c>
       <c r="M40" s="17">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="N40" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>220</v>
-      </c>
-      <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B40, $C$2:$C$628, C40, $D$2:$D$628, D40, $E$2:$E$628, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25324,11 +25337,11 @@
         <v>8239</v>
       </c>
       <c r="M41" s="17">
+        <f t="shared" si="1"/>
+        <v>528</v>
+      </c>
+      <c r="N41" t="str">
         <f t="shared" si="0"/>
-        <v>528</v>
-      </c>
-      <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B41, $C$2:$C$628, C41, $D$2:$D$628, D41, $E$2:$E$628, E41) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25370,11 +25383,11 @@
         <v>3395</v>
       </c>
       <c r="M42" s="17">
+        <f t="shared" si="1"/>
+        <v>295</v>
+      </c>
+      <c r="N42" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>295</v>
-      </c>
-      <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B42, $C$2:$C$628, C42, $D$2:$D$628, D42, $E$2:$E$628, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25417,11 +25430,11 @@
         <v>5382</v>
       </c>
       <c r="M43" s="17">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="N43" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>540</v>
-      </c>
-      <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B43, $C$2:$C$628, C43, $D$2:$D$628, D43, $E$2:$E$628, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -25465,11 +25478,11 @@
         <v>3810</v>
       </c>
       <c r="M44" s="17">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="N44" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>250</v>
-      </c>
-      <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B44, $C$2:$C$628, C44, $D$2:$D$628, D44, $E$2:$E$628, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25506,7 +25519,7 @@
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B45, $C$2:$C$628, C45, $D$2:$D$628, D45, $E$2:$E$628, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -25547,7 +25560,7 @@
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B46, $C$2:$C$628, C46, $D$2:$D$628, D46, $E$2:$E$628, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -25595,7 +25608,7 @@
         <v>300</v>
       </c>
       <c r="N47" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B47, $C$2:$C$628, C47, $D$2:$D$628, D47, $E$2:$E$628, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25642,7 +25655,7 @@
         <v>448</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B48, $C$2:$C$628, C48, $D$2:$D$628, D48, $E$2:$E$628, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25681,7 +25694,7 @@
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B49, $C$2:$C$628, C49, $D$2:$D$628, D49, $E$2:$E$628, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -25720,7 +25733,7 @@
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B50, $C$2:$C$628, C50, $D$2:$D$628, D50, $E$2:$E$628, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -25769,7 +25782,7 @@
         <v>225</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B51, $C$2:$C$628, C51, $D$2:$D$628, D51, $E$2:$E$628, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25806,7 +25819,7 @@
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B52, $C$2:$C$628, C52, $D$2:$D$628, D52, $E$2:$E$628, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -25854,7 +25867,7 @@
         <v>660</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B53, $C$2:$C$628, C53, $D$2:$D$628, D53, $E$2:$E$628, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25900,7 +25913,7 @@
         <v>250</v>
       </c>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B54, $C$2:$C$628, C54, $D$2:$D$628, D54, $E$2:$E$628, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25937,7 +25950,7 @@
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B55, $C$2:$C$628, C55, $D$2:$D$628, D55, $E$2:$E$628, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -25985,7 +25998,7 @@
         <v>240</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B56, $C$2:$C$628, C56, $D$2:$D$628, D56, $E$2:$E$628, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26022,7 +26035,7 @@
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B57, $C$2:$C$628, C57, $D$2:$D$628, D57, $E$2:$E$628, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -26070,7 +26083,7 @@
         <v>264</v>
       </c>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B58, $C$2:$C$628, C58, $D$2:$D$628, D58, $E$2:$E$628, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26107,7 +26120,7 @@
       <c r="L59" s="16"/>
       <c r="M59" s="16"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B59, $C$2:$C$628, C59, $D$2:$D$628, D59, $E$2:$E$628, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -26155,7 +26168,7 @@
         <v>360</v>
       </c>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B60, $C$2:$C$628, C60, $D$2:$D$628, D60, $E$2:$E$628, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26192,7 +26205,7 @@
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B61, $C$2:$C$628, C61, $D$2:$D$628, D61, $E$2:$E$628, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -26240,7 +26253,7 @@
         <v>1450</v>
       </c>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B62, $C$2:$C$628, C62, $D$2:$D$628, D62, $E$2:$E$628, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26277,7 +26290,7 @@
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B63, $C$2:$C$628, C63, $D$2:$D$628, D63, $E$2:$E$628, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -26325,7 +26338,7 @@
         <v>250</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B64, $C$2:$C$628, C64, $D$2:$D$628, D64, $E$2:$E$628, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26364,7 +26377,7 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B65, $C$2:$C$628, C65, $D$2:$D$628, D65, $E$2:$E$628, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -26409,11 +26422,11 @@
         <v>34840</v>
       </c>
       <c r="M66" s="17">
-        <f t="shared" ref="M66:M73" si="1">ABS((D66*E66)-L66)</f>
+        <f t="shared" ref="M66:M73" si="2">ABS((D66*E66)-L66)</f>
         <v>920</v>
       </c>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B66, $C$2:$C$628, C66, $D$2:$D$628, D66, $E$2:$E$628, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="3">IF(COUNTIFS( $B$2:$B$628, B66, $C$2:$C$628, C66, $D$2:$D$628, D66, $E$2:$E$628, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26455,11 +26468,11 @@
         <v>17017</v>
       </c>
       <c r="M67" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1300</v>
       </c>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B67, $C$2:$C$628, C67, $D$2:$D$628, D67, $E$2:$E$628, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26501,11 +26514,11 @@
         <v>32400</v>
       </c>
       <c r="M68" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B68, $C$2:$C$628, C68, $D$2:$D$628, D68, $E$2:$E$628, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26547,11 +26560,11 @@
         <v>14560</v>
       </c>
       <c r="M69" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B69, $C$2:$C$628, C69, $D$2:$D$628, D69, $E$2:$E$628, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26593,11 +26606,11 @@
         <v>6868</v>
       </c>
       <c r="M70" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B70, $C$2:$C$628, C70, $D$2:$D$628, D70, $E$2:$E$628, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26640,11 +26653,11 @@
         <v>8710</v>
       </c>
       <c r="M71" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>260</v>
       </c>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B71, $C$2:$C$628, C71, $D$2:$D$628, D71, $E$2:$E$628, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="10"/>
@@ -26688,11 +26701,11 @@
         <v>13884</v>
       </c>
       <c r="M72" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>660</v>
       </c>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B72, $C$2:$C$628, C72, $D$2:$D$628, D72, $E$2:$E$628, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26734,11 +26747,11 @@
         <v>17020</v>
       </c>
       <c r="M73" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B73, $C$2:$C$628, C73, $D$2:$D$628, D73, $E$2:$E$628, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26774,7 +26787,7 @@
         <v>117</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B74, $C$2:$C$628, C74, $D$2:$D$628, D74, $E$2:$E$628, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26821,7 +26834,7 @@
         <v>200</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B75, $C$2:$C$628, C75, $D$2:$D$628, D75, $E$2:$E$628, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26867,7 +26880,7 @@
         <v>800</v>
       </c>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B76, $C$2:$C$628, C76, $D$2:$D$628, D76, $E$2:$E$628, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="10"/>
@@ -26915,7 +26928,7 @@
         <v>1200</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B77, $C$2:$C$628, C77, $D$2:$D$628, D77, $E$2:$E$628, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="36" t="s">
@@ -26964,7 +26977,7 @@
         <v>650</v>
       </c>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B78, $C$2:$C$628, C78, $D$2:$D$628, D78, $E$2:$E$628, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27010,7 +27023,7 @@
         <v>700</v>
       </c>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B79, $C$2:$C$628, C79, $D$2:$D$628, D79, $E$2:$E$628, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27049,7 +27062,7 @@
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B80, $C$2:$C$628, C80, $D$2:$D$628, D80, $E$2:$E$628, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="10"/>
@@ -27090,7 +27103,7 @@
       <c r="L81" s="16"/>
       <c r="M81" s="16"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B81, $C$2:$C$628, C81, $D$2:$D$628, D81, $E$2:$E$628, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O81"/>
@@ -27134,11 +27147,11 @@
         <v>14050</v>
       </c>
       <c r="M82" s="17">
-        <f t="shared" ref="M82:M100" si="2">ABS((D82*E82)-L82)</f>
+        <f t="shared" ref="M82:M100" si="4">ABS((D82*E82)-L82)</f>
         <v>400</v>
       </c>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B82, $C$2:$C$628, C82, $D$2:$D$628, D82, $E$2:$E$628, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27180,11 +27193,11 @@
         <v>18495</v>
       </c>
       <c r="M83" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B83, $C$2:$C$628, C83, $D$2:$D$628, D83, $E$2:$E$628, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27227,11 +27240,11 @@
         <v>8870</v>
       </c>
       <c r="M84" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B84, $C$2:$C$628, C84, $D$2:$D$628, D84, $E$2:$E$628, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="36" t="s">
@@ -27276,11 +27289,11 @@
         <v>8700</v>
       </c>
       <c r="M85" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B85, $C$2:$C$628, C85, $D$2:$D$628, D85, $E$2:$E$628, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27322,11 +27335,11 @@
         <v>3450</v>
       </c>
       <c r="M86" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B86, $C$2:$C$628, C86, $D$2:$D$628, D86, $E$2:$E$628, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="10"/>
@@ -27370,11 +27383,11 @@
         <v>8220</v>
       </c>
       <c r="M87" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B87, $C$2:$C$628, C87, $D$2:$D$628, D87, $E$2:$E$628, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="36" t="s">
@@ -27420,11 +27433,11 @@
         <v>32900</v>
       </c>
       <c r="M88" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1000</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B88, $C$2:$C$628, C88, $D$2:$D$628, D88, $E$2:$E$628, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="10"/>
@@ -27468,11 +27481,11 @@
         <v>6127.5</v>
       </c>
       <c r="M89" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>612.5</v>
       </c>
       <c r="N89" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B89, $C$2:$C$628, C89, $D$2:$D$628, D89, $E$2:$E$628, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="27"/>
@@ -27516,11 +27529,11 @@
         <v>6320</v>
       </c>
       <c r="M90" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>420</v>
       </c>
       <c r="N90" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B90, $C$2:$C$628, C90, $D$2:$D$628, D90, $E$2:$E$628, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O90" s="27"/>
@@ -27564,11 +27577,11 @@
         <v>14310</v>
       </c>
       <c r="M91" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>660</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B91, $C$2:$C$628, C91, $D$2:$D$628, D91, $E$2:$E$628, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27610,11 +27623,11 @@
         <v>19395</v>
       </c>
       <c r="M92" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B92, $C$2:$C$628, C92, $D$2:$D$628, D92, $E$2:$E$628, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27657,11 +27670,11 @@
         <v>8970</v>
       </c>
       <c r="M93" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B93, $C$2:$C$628, C93, $D$2:$D$628, D93, $E$2:$E$628, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27697,11 +27710,11 @@
         <v>40</v>
       </c>
       <c r="M94" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3156</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B94, $C$2:$C$628, C94, $D$2:$D$628, D94, $E$2:$E$628, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P94" s="18"/>
@@ -27744,11 +27757,11 @@
         <v>16755</v>
       </c>
       <c r="M95" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B95, $C$2:$C$628, C95, $D$2:$D$628, D95, $E$2:$E$628, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27790,11 +27803,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M96" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>11409.000000000004</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B96, $C$2:$C$628, C96, $D$2:$D$628, D96, $E$2:$E$628, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P96"/>
@@ -27837,11 +27850,11 @@
         <v>8420</v>
       </c>
       <c r="M97" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B97, $C$2:$C$628, C97, $D$2:$D$628, D97, $E$2:$E$628, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27883,11 +27896,11 @@
         <v>5620</v>
       </c>
       <c r="M98" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B98, $C$2:$C$628, C98, $D$2:$D$628, D98, $E$2:$E$628, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="10"/>
@@ -27931,11 +27944,11 @@
         <v>8570</v>
       </c>
       <c r="M99" s="25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B99, $C$2:$C$628, C99, $D$2:$D$628, D99, $E$2:$E$628, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="36" t="s">
@@ -27981,11 +27994,11 @@
         <v>33200</v>
       </c>
       <c r="M100" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B100, $C$2:$C$628, C100, $D$2:$D$628, D100, $E$2:$E$628, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28022,7 +28035,7 @@
       <c r="L101" s="16"/>
       <c r="M101" s="16"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B101, $C$2:$C$628, C101, $D$2:$D$628, D101, $E$2:$E$628, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O101"/>
@@ -28070,7 +28083,7 @@
         <v>200</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B102, $C$2:$C$628, C102, $D$2:$D$628, D102, $E$2:$E$628, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28116,7 +28129,7 @@
         <v>880</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B103, $C$2:$C$628, C103, $D$2:$D$628, D103, $E$2:$E$628, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="36" t="s">
@@ -28165,7 +28178,7 @@
         <v>645</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B104, $C$2:$C$628, C104, $D$2:$D$628, D104, $E$2:$E$628, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="36" t="s">
@@ -28214,7 +28227,7 @@
         <v>390</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B105, $C$2:$C$628, C105, $D$2:$D$628, D105, $E$2:$E$628, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28251,7 +28264,7 @@
       <c r="L106" s="16"/>
       <c r="M106" s="16"/>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B106, $C$2:$C$628, C106, $D$2:$D$628, D106, $E$2:$E$628, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O106"/>
@@ -28295,11 +28308,11 @@
         <v>39300</v>
       </c>
       <c r="M107" s="17">
-        <f t="shared" ref="M107:M112" si="3">ABS((D107*E107)-L107)</f>
+        <f t="shared" ref="M107:M112" si="5">ABS((D107*E107)-L107)</f>
         <v>18850</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B107, $C$2:$C$628, C107, $D$2:$D$628, D107, $E$2:$E$628, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28341,11 +28354,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M108" s="17">
+        <f t="shared" si="5"/>
+        <v>14149.000000000004</v>
+      </c>
+      <c r="N108" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>14149.000000000004</v>
-      </c>
-      <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B108, $C$2:$C$628, C108, $D$2:$D$628, D108, $E$2:$E$628, E108) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P108"/>
@@ -28388,11 +28401,11 @@
         <v>9170</v>
       </c>
       <c r="M109" s="25">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N109" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B109, $C$2:$C$628, C109, $D$2:$D$628, D109, $E$2:$E$628, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28434,11 +28447,11 @@
         <v>33950</v>
       </c>
       <c r="M110" s="17">
+        <f t="shared" si="5"/>
+        <v>850</v>
+      </c>
+      <c r="N110" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>850</v>
-      </c>
-      <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B110, $C$2:$C$628, C110, $D$2:$D$628, D110, $E$2:$E$628, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O110" s="10"/>
@@ -28482,11 +28495,11 @@
         <v>17150</v>
       </c>
       <c r="M111" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N111" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B111, $C$2:$C$628, C111, $D$2:$D$628, D111, $E$2:$E$628, E111) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28528,11 +28541,11 @@
         <v>10300</v>
       </c>
       <c r="M112" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N112" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B112, $C$2:$C$628, C112, $D$2:$D$628, D112, $E$2:$E$628, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P112" s="27"/>
@@ -28567,7 +28580,7 @@
       </c>
       <c r="J113" s="32"/>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B113, $C$2:$C$628, C113, $D$2:$D$628, D113, $E$2:$E$628, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28613,7 +28626,7 @@
         <v>654.5</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B114, $C$2:$C$628, C114, $D$2:$D$628, D114, $E$2:$E$628, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="36" t="s">
@@ -28662,7 +28675,7 @@
         <v>274</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B115, $C$2:$C$628, C115, $D$2:$D$628, D115, $E$2:$E$628, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="10"/>
@@ -28710,7 +28723,7 @@
         <v>650</v>
       </c>
       <c r="N116" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B116, $C$2:$C$628, C116, $D$2:$D$628, D116, $E$2:$E$628, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28756,7 +28769,7 @@
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B117, $C$2:$C$628, C117, $D$2:$D$628, D117, $E$2:$E$628, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P117" s="18"/>
@@ -28793,7 +28806,7 @@
         <v>116</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B118, $C$2:$C$628, C118, $D$2:$D$628, D118, $E$2:$E$628, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28839,7 +28852,7 @@
         <v>650</v>
       </c>
       <c r="N119" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B119, $C$2:$C$628, C119, $D$2:$D$628, D119, $E$2:$E$628, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="27"/>
@@ -28887,7 +28900,7 @@
         <v>934</v>
       </c>
       <c r="N120" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B120, $C$2:$C$628, C120, $D$2:$D$628, D120, $E$2:$E$628, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="27"/>
@@ -28935,7 +28948,7 @@
         <v>300</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B121, $C$2:$C$628, C121, $D$2:$D$628, D121, $E$2:$E$628, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="27"/>
@@ -28982,7 +28995,7 @@
         <v>265</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B122, $C$2:$C$628, C122, $D$2:$D$628, D122, $E$2:$E$628, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29028,7 +29041,7 @@
         <v>654</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B123, $C$2:$C$628, C123, $D$2:$D$628, D123, $E$2:$E$628, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="36" t="s">
@@ -29070,7 +29083,7 @@
         <v>143</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B124, $C$2:$C$628, C124, $D$2:$D$628, D124, $E$2:$E$628, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29116,7 +29129,7 @@
         <v>1400</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B125, $C$2:$C$628, C125, $D$2:$D$628, D125, $E$2:$E$628, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="36" t="s">
@@ -29165,7 +29178,7 @@
         <v>276</v>
       </c>
       <c r="N126" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B126, $C$2:$C$628, C126, $D$2:$D$628, D126, $E$2:$E$628, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29211,7 +29224,7 @@
         <v>504.5</v>
       </c>
       <c r="N127" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B127, $C$2:$C$628, C127, $D$2:$D$628, D127, $E$2:$E$628, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O127" s="36" t="s">
@@ -29261,7 +29274,7 @@
         <v>545</v>
       </c>
       <c r="N128" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B128, $C$2:$C$628, C128, $D$2:$D$628, D128, $E$2:$E$628, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O128" s="36" t="s">
@@ -29304,7 +29317,7 @@
       <c r="L129" s="16"/>
       <c r="M129" s="16"/>
       <c r="N129" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B129, $C$2:$C$628, C129, $D$2:$D$628, D129, $E$2:$E$628, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="37" t="s">
@@ -29354,7 +29367,7 @@
         <v>656.5</v>
       </c>
       <c r="N130" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B130, $C$2:$C$628, C130, $D$2:$D$628, D130, $E$2:$E$628, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$628, B130, $C$2:$C$628, C130, $D$2:$D$628, D130, $E$2:$E$628, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -29400,7 +29413,7 @@
         <v>300</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B131, $C$2:$C$628, C131, $D$2:$D$628, D131, $E$2:$E$628, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29436,7 +29449,7 @@
         <v>117</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B132, $C$2:$C$628, C132, $D$2:$D$628, D132, $E$2:$E$628, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29483,7 +29496,7 @@
         <v>444</v>
       </c>
       <c r="N133" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B133, $C$2:$C$628, C133, $D$2:$D$628, D133, $E$2:$E$628, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29529,7 +29542,7 @@
         <v>300</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B134, $C$2:$C$628, C134, $D$2:$D$628, D134, $E$2:$E$628, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="10"/>
@@ -29577,7 +29590,7 @@
         <v>18350</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B135, $C$2:$C$628, C135, $D$2:$D$628, D135, $E$2:$E$628, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29623,7 +29636,7 @@
         <v>650</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B136, $C$2:$C$628, C136, $D$2:$D$628, D136, $E$2:$E$628, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29659,7 +29672,7 @@
         <v>117</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B137, $C$2:$C$628, C137, $D$2:$D$628, D137, $E$2:$E$628, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29693,7 +29706,7 @@
       </c>
       <c r="J138" s="32"/>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B138, $C$2:$C$628, C138, $D$2:$D$628, D138, $E$2:$E$628, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="27"/>
@@ -29728,7 +29741,7 @@
       </c>
       <c r="J139" s="32"/>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B139, $C$2:$C$628, C139, $D$2:$D$628, D139, $E$2:$E$628, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P139" s="27"/>
@@ -29771,11 +29784,11 @@
         <v>34100</v>
       </c>
       <c r="M140" s="17">
-        <f t="shared" ref="M140:M145" si="4">ABS((D140*E140)-L140)</f>
+        <f t="shared" ref="M140:M145" si="7">ABS((D140*E140)-L140)</f>
         <v>1700</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B140, $C$2:$C$628, C140, $D$2:$D$628, D140, $E$2:$E$628, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="27"/>
@@ -29818,11 +29831,11 @@
         <v>7578</v>
       </c>
       <c r="M141" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>294</v>
       </c>
       <c r="N141" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B141, $C$2:$C$628, C141, $D$2:$D$628, D141, $E$2:$E$628, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29864,11 +29877,11 @@
         <v>7578</v>
       </c>
       <c r="M142" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>294</v>
       </c>
       <c r="N142" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B142, $C$2:$C$628, C142, $D$2:$D$628, D142, $E$2:$E$628, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O142" s="10"/>
@@ -29912,11 +29925,11 @@
         <v>4968</v>
       </c>
       <c r="M143" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>280</v>
       </c>
       <c r="N143" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B143, $C$2:$C$628, C143, $D$2:$D$628, D143, $E$2:$E$628, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="27"/>
@@ -29960,11 +29973,11 @@
         <v>37480</v>
       </c>
       <c r="M144" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1000</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B144, $C$2:$C$628, C144, $D$2:$D$628, D144, $E$2:$E$628, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P144" s="27"/>
@@ -30007,11 +30020,11 @@
         <v>20010</v>
       </c>
       <c r="M145" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B145, $C$2:$C$628, C145, $D$2:$D$628, D145, $E$2:$E$628, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P145"/>
@@ -30048,7 +30061,7 @@
         <v>116</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B146, $C$2:$C$628, C146, $D$2:$D$628, D146, $E$2:$E$628, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30082,7 +30095,7 @@
       </c>
       <c r="J147" s="32"/>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B147, $C$2:$C$628, C147, $D$2:$D$628, D147, $E$2:$E$628, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30128,7 +30141,7 @@
         <v>300</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B148, $C$2:$C$628, C148, $D$2:$D$628, D148, $E$2:$E$628, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30174,7 +30187,7 @@
         <v>646</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B149, $C$2:$C$628, C149, $D$2:$D$628, D149, $E$2:$E$628, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="36" t="s">
@@ -30216,7 +30229,7 @@
       <c r="L150" s="16"/>
       <c r="M150" s="16"/>
       <c r="N150" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B150, $C$2:$C$628, C150, $D$2:$D$628, D150, $E$2:$E$628, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O150"/>
@@ -30264,7 +30277,7 @@
         <v>500</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B151, $C$2:$C$628, C151, $D$2:$D$628, D151, $E$2:$E$628, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="37" t="s">
@@ -30313,7 +30326,7 @@
         <v>300</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B152, $C$2:$C$628, C152, $D$2:$D$628, D152, $E$2:$E$628, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O152"/>
@@ -30351,7 +30364,7 @@
         <v>117</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B153, $C$2:$C$628, C153, $D$2:$D$628, D153, $E$2:$E$628, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30397,7 +30410,7 @@
         <v>800</v>
       </c>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B154, $C$2:$C$628, C154, $D$2:$D$628, D154, $E$2:$E$628, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30431,7 +30444,7 @@
       </c>
       <c r="J155" s="32"/>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B155, $C$2:$C$628, C155, $D$2:$D$628, D155, $E$2:$E$628, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="36" t="s">
@@ -30474,7 +30487,7 @@
       <c r="L156" s="16"/>
       <c r="M156" s="16"/>
       <c r="N156" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B156, $C$2:$C$628, C156, $D$2:$D$628, D156, $E$2:$E$628, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O156"/>
@@ -30510,7 +30523,7 @@
       </c>
       <c r="J157" s="32"/>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B157, $C$2:$C$628, C157, $D$2:$D$628, D157, $E$2:$E$628, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30544,7 +30557,7 @@
       </c>
       <c r="J158" s="32"/>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B158, $C$2:$C$628, C158, $D$2:$D$628, D158, $E$2:$E$628, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30590,7 +30603,7 @@
         <v>270</v>
       </c>
       <c r="N159" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B159, $C$2:$C$628, C159, $D$2:$D$628, D159, $E$2:$E$628, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="37" t="s">
@@ -30640,7 +30653,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N160" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B160, $C$2:$C$628, C160, $D$2:$D$628, D160, $E$2:$E$628, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="37" t="s">
@@ -30690,7 +30703,7 @@
         <v>940</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B161, $C$2:$C$628, C161, $D$2:$D$628, D161, $E$2:$E$628, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30736,7 +30749,7 @@
         <v>300</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B162, $C$2:$C$628, C162, $D$2:$D$628, D162, $E$2:$E$628, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30782,7 +30795,7 @@
         <v>650</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B163, $C$2:$C$628, C163, $D$2:$D$628, D163, $E$2:$E$628, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="27"/>
@@ -30819,7 +30832,7 @@
         <v>117</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B164, $C$2:$C$628, C164, $D$2:$D$628, D164, $E$2:$E$628, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O164" s="36" t="s">
@@ -30858,7 +30871,7 @@
         <v>117</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B165, $C$2:$C$628, C165, $D$2:$D$628, D165, $E$2:$E$628, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30892,7 +30905,7 @@
       </c>
       <c r="J166" s="32"/>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B166, $C$2:$C$628, C166, $D$2:$D$628, D166, $E$2:$E$628, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="22"/>
@@ -30929,7 +30942,7 @@
         <v>117</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B167, $C$2:$C$628, C167, $D$2:$D$628, D167, $E$2:$E$628, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30965,7 +30978,7 @@
         <v>116</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B168, $C$2:$C$628, C168, $D$2:$D$628, D168, $E$2:$E$628, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31011,7 +31024,7 @@
         <v>300</v>
       </c>
       <c r="N169" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B169, $C$2:$C$628, C169, $D$2:$D$628, D169, $E$2:$E$628, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31057,7 +31070,7 @@
         <v>260</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B170, $C$2:$C$628, C170, $D$2:$D$628, D170, $E$2:$E$628, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31103,7 +31116,7 @@
         <v>271.80000000000018</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B171, $C$2:$C$628, C171, $D$2:$D$628, D171, $E$2:$E$628, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31149,7 +31162,7 @@
         <v>300</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B172, $C$2:$C$628, C172, $D$2:$D$628, D172, $E$2:$E$628, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31183,7 +31196,7 @@
       </c>
       <c r="J173" s="32"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B173, $C$2:$C$628, C173, $D$2:$D$628, D173, $E$2:$E$628, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31229,7 +31242,7 @@
         <v>395</v>
       </c>
       <c r="N174" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B174, $C$2:$C$628, C174, $D$2:$D$628, D174, $E$2:$E$628, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O174" s="36" t="s">
@@ -31279,7 +31292,7 @@
         <v>250</v>
       </c>
       <c r="N175" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B175, $C$2:$C$628, C175, $D$2:$D$628, D175, $E$2:$E$628, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O175" s="36" t="s">
@@ -31317,7 +31330,7 @@
       </c>
       <c r="J176" s="32"/>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B176, $C$2:$C$628, C176, $D$2:$D$628, D176, $E$2:$E$628, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31353,7 +31366,7 @@
         <v>117</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B177, $C$2:$C$628, C177, $D$2:$D$628, D177, $E$2:$E$628, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31399,7 +31412,7 @@
         <v>500</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B178, $C$2:$C$628, C178, $D$2:$D$628, D178, $E$2:$E$628, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31433,7 +31446,7 @@
       </c>
       <c r="J179" s="32"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B179, $C$2:$C$628, C179, $D$2:$D$628, D179, $E$2:$E$628, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P179" s="27"/>
@@ -31480,7 +31493,7 @@
         <v>376</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B180, $C$2:$C$628, C180, $D$2:$D$628, D180, $E$2:$E$628, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="10"/>
@@ -31521,7 +31534,7 @@
       <c r="L181" s="17"/>
       <c r="M181" s="17"/>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B181, $C$2:$C$628, C181, $D$2:$D$628, D181, $E$2:$E$628, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="10"/>
@@ -31559,7 +31572,7 @@
         <v>116</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B182, $C$2:$C$628, C182, $D$2:$D$628, D182, $E$2:$E$628, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31605,7 +31618,7 @@
         <v>650</v>
       </c>
       <c r="N183" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B183, $C$2:$C$628, C183, $D$2:$D$628, D183, $E$2:$E$628, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P183" s="27"/>
@@ -31642,7 +31655,7 @@
         <v>116</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B184, $C$2:$C$628, C184, $D$2:$D$628, D184, $E$2:$E$628, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31684,11 +31697,11 @@
         <v>5180</v>
       </c>
       <c r="M185" s="40">
-        <f t="shared" ref="M185:M192" si="5">ABS((D185*E185)-L185)</f>
+        <f t="shared" ref="M185:M192" si="8">ABS((D185*E185)-L185)</f>
         <v>268</v>
       </c>
       <c r="N185" s="53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B185, $C$2:$C$628, C185, $D$2:$D$628, D185, $E$2:$E$628, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="22"/>
@@ -31734,11 +31747,11 @@
         <v>11660</v>
       </c>
       <c r="M186" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B186, $C$2:$C$628, C186, $D$2:$D$628, D186, $E$2:$E$628, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="36" t="s">
@@ -31783,11 +31796,11 @@
         <v>10250</v>
       </c>
       <c r="M187" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B187, $C$2:$C$628, C187, $D$2:$D$628, D187, $E$2:$E$628, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31829,11 +31842,11 @@
         <v>5755</v>
       </c>
       <c r="M188" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>275</v>
       </c>
       <c r="N188" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B188, $C$2:$C$628, C188, $D$2:$D$628, D188, $E$2:$E$628, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31875,11 +31888,11 @@
         <v>5805</v>
       </c>
       <c r="M189" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>225</v>
       </c>
       <c r="N189" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B189, $C$2:$C$628, C189, $D$2:$D$628, D189, $E$2:$E$628, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31921,11 +31934,11 @@
         <v>5520</v>
       </c>
       <c r="M190" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N190" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B190, $C$2:$C$628, C190, $D$2:$D$628, D190, $E$2:$E$628, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="36" t="s">
@@ -31970,11 +31983,11 @@
         <v>2657</v>
       </c>
       <c r="M191" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>253</v>
       </c>
       <c r="N191" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B191, $C$2:$C$628, C191, $D$2:$D$628, D191, $E$2:$E$628, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O191" s="36" t="s">
@@ -32020,11 +32033,11 @@
         <v>2554.5</v>
       </c>
       <c r="M192" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>355.5</v>
       </c>
       <c r="N192" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B192, $C$2:$C$628, C192, $D$2:$D$628, D192, $E$2:$E$628, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O192" s="36" t="s">
@@ -32062,7 +32075,7 @@
       </c>
       <c r="J193" s="32"/>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B193, $C$2:$C$628, C193, $D$2:$D$628, D193, $E$2:$E$628, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32096,7 +32109,7 @@
       </c>
       <c r="J194" s="32"/>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B194, $C$2:$C$628, C194, $D$2:$D$628, D194, $E$2:$E$628, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$628, B194, $C$2:$C$628, C194, $D$2:$D$628, D194, $E$2:$E$628, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -32135,7 +32148,7 @@
       <c r="L195" s="17"/>
       <c r="M195" s="17"/>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B195, $C$2:$C$628, C195, $D$2:$D$628, D195, $E$2:$E$628, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P195" s="10"/>
@@ -32182,7 +32195,7 @@
         <v>501</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B196, $C$2:$C$628, C196, $D$2:$D$628, D196, $E$2:$E$628, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="36" t="s">
@@ -32231,7 +32244,7 @@
         <v>650</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B197, $C$2:$C$628, C197, $D$2:$D$628, D197, $E$2:$E$628, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P197" s="27"/>
@@ -32278,7 +32291,7 @@
         <v>10680</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B198, $C$2:$C$628, C198, $D$2:$D$628, D198, $E$2:$E$628, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32312,7 +32325,7 @@
       </c>
       <c r="J199" s="32"/>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B199, $C$2:$C$628, C199, $D$2:$D$628, D199, $E$2:$E$628, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32351,7 +32364,7 @@
       <c r="L200" s="17"/>
       <c r="M200" s="17"/>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B200, $C$2:$C$628, C200, $D$2:$D$628, D200, $E$2:$E$628, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P200" s="10"/>
@@ -32389,7 +32402,7 @@
       <c r="L201" s="17"/>
       <c r="M201" s="17"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B201, $C$2:$C$628, C201, $D$2:$D$628, D201, $E$2:$E$628, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="10"/>
@@ -32430,7 +32443,7 @@
       <c r="L202" s="16"/>
       <c r="M202" s="16"/>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B202, $C$2:$C$628, C202, $D$2:$D$628, D202, $E$2:$E$628, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O202"/>
@@ -32477,7 +32490,7 @@
         <v>250</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B203, $C$2:$C$628, C203, $D$2:$D$628, D203, $E$2:$E$628, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="10"/>
@@ -32525,7 +32538,7 @@
         <v>300</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B204, $C$2:$C$628, C204, $D$2:$D$628, D204, $E$2:$E$628, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32564,7 +32577,7 @@
       <c r="L205" s="17"/>
       <c r="M205" s="17"/>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B205, $C$2:$C$628, C205, $D$2:$D$628, D205, $E$2:$E$628, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="10"/>
@@ -32603,7 +32616,7 @@
       <c r="L206" s="17"/>
       <c r="M206" s="17"/>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B206, $C$2:$C$628, C206, $D$2:$D$628, D206, $E$2:$E$628, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="10"/>
@@ -32651,7 +32664,7 @@
         <v>527.5</v>
       </c>
       <c r="N207" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B207, $C$2:$C$628, C207, $D$2:$D$628, D207, $E$2:$E$628, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="27"/>
@@ -32694,7 +32707,7 @@
       <c r="L208" s="25"/>
       <c r="M208" s="25"/>
       <c r="N208" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B208, $C$2:$C$628, C208, $D$2:$D$628, D208, $E$2:$E$628, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="27"/>
@@ -32742,7 +32755,7 @@
         <v>290</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B209, $C$2:$C$628, C209, $D$2:$D$628, D209, $E$2:$E$628, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32788,7 +32801,7 @@
         <v>300</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B210, $C$2:$C$628, C210, $D$2:$D$628, D210, $E$2:$E$628, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="10"/>
@@ -32836,7 +32849,7 @@
         <v>250</v>
       </c>
       <c r="N211" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B211, $C$2:$C$628, C211, $D$2:$D$628, D211, $E$2:$E$628, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O211" s="10"/>
@@ -32884,7 +32897,7 @@
         <v>300</v>
       </c>
       <c r="N212" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B212, $C$2:$C$628, C212, $D$2:$D$628, D212, $E$2:$E$628, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="27"/>
@@ -32932,7 +32945,7 @@
         <v>188</v>
       </c>
       <c r="N213" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B213, $C$2:$C$628, C213, $D$2:$D$628, D213, $E$2:$E$628, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="27"/>
@@ -32970,7 +32983,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B214, $C$2:$C$628, C214, $D$2:$D$628, D214, $E$2:$E$628, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="27"/>
@@ -33005,7 +33018,7 @@
       </c>
       <c r="J215" s="32"/>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B215, $C$2:$C$628, C215, $D$2:$D$628, D215, $E$2:$E$628, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33051,7 +33064,7 @@
         <v>10880</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B216, $C$2:$C$628, C216, $D$2:$D$628, D216, $E$2:$E$628, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33087,7 +33100,7 @@
         <v>116</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B217, $C$2:$C$628, C217, $D$2:$D$628, D217, $E$2:$E$628, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33123,7 +33136,7 @@
         <v>116</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B218, $C$2:$C$628, C218, $D$2:$D$628, D218, $E$2:$E$628, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="27"/>
@@ -33170,7 +33183,7 @@
         <v>275</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B219, $C$2:$C$628, C219, $D$2:$D$628, D219, $E$2:$E$628, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33216,7 +33229,7 @@
         <v>500</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B220, $C$2:$C$628, C220, $D$2:$D$628, D220, $E$2:$E$628, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33262,7 +33275,7 @@
         <v>360</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B221, $C$2:$C$628, C221, $D$2:$D$628, D221, $E$2:$E$628, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -33303,7 +33316,7 @@
       <c r="L222" s="17"/>
       <c r="M222" s="17"/>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B222, $C$2:$C$628, C222, $D$2:$D$628, D222, $E$2:$E$628, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="10"/>
@@ -33339,7 +33352,7 @@
       </c>
       <c r="J223" s="32"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B223, $C$2:$C$628, C223, $D$2:$D$628, D223, $E$2:$E$628, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33375,7 +33388,7 @@
         <v>117</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B224, $C$2:$C$628, C224, $D$2:$D$628, D224, $E$2:$E$628, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33421,7 +33434,7 @@
         <v>320</v>
       </c>
       <c r="N225" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B225, $C$2:$C$628, C225, $D$2:$D$628, D225, $E$2:$E$628, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="27"/>
@@ -33469,7 +33482,7 @@
         <v>448</v>
       </c>
       <c r="N226" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B226, $C$2:$C$628, C226, $D$2:$D$628, D226, $E$2:$E$628, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="27"/>
@@ -33517,7 +33530,7 @@
         <v>500</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B227, $C$2:$C$628, C227, $D$2:$D$628, D227, $E$2:$E$628, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33553,7 +33566,7 @@
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B228, $C$2:$C$628, C228, $D$2:$D$628, D228, $E$2:$E$628, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33587,7 +33600,7 @@
       </c>
       <c r="J229" s="32"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B229, $C$2:$C$628, C229, $D$2:$D$628, D229, $E$2:$E$628, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33621,7 +33634,7 @@
       </c>
       <c r="J230" s="32"/>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B230, $C$2:$C$628, C230, $D$2:$D$628, D230, $E$2:$E$628, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="27"/>
@@ -33668,7 +33681,7 @@
         <v>816</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B231, $C$2:$C$628, C231, $D$2:$D$628, D231, $E$2:$E$628, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33714,7 +33727,7 @@
         <v>150</v>
       </c>
       <c r="N232" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B232, $C$2:$C$628, C232, $D$2:$D$628, D232, $E$2:$E$628, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -33760,7 +33773,7 @@
         <v>250</v>
       </c>
       <c r="N233" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B233, $C$2:$C$628, C233, $D$2:$D$628, D233, $E$2:$E$628, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -33806,7 +33819,7 @@
         <v>280</v>
       </c>
       <c r="N234" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B234, $C$2:$C$628, C234, $D$2:$D$628, D234, $E$2:$E$628, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33852,7 +33865,7 @@
         <v>800</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B235, $C$2:$C$628, C235, $D$2:$D$628, D235, $E$2:$E$628, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="36" t="s">
@@ -33891,7 +33904,7 @@
         <v>54</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B236, $C$2:$C$628, C236, $D$2:$D$628, D236, $E$2:$E$628, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33937,7 +33950,7 @@
         <v>300</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B237, $C$2:$C$628, C237, $D$2:$D$628, D237, $E$2:$E$628, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33983,7 +33996,7 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B238, $C$2:$C$628, C238, $D$2:$D$628, D238, $E$2:$E$628, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34029,7 +34042,7 @@
         <v>260</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B239, $C$2:$C$628, C239, $D$2:$D$628, D239, $E$2:$E$628, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34075,7 +34088,7 @@
         <v>400</v>
       </c>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B240, $C$2:$C$628, C240, $D$2:$D$628, D240, $E$2:$E$628, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34121,7 +34134,7 @@
         <v>500</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B241, $C$2:$C$628, C241, $D$2:$D$628, D241, $E$2:$E$628, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34157,7 +34170,7 @@
         <v>117</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B242, $C$2:$C$628, C242, $D$2:$D$628, D242, $E$2:$E$628, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34191,7 +34204,7 @@
       </c>
       <c r="J243" s="32"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B243, $C$2:$C$628, C243, $D$2:$D$628, D243, $E$2:$E$628, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34237,7 +34250,7 @@
         <v>140</v>
       </c>
       <c r="N244" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B244, $C$2:$C$628, C244, $D$2:$D$628, D244, $E$2:$E$628, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
       <c r="O244" s="10"/>
@@ -34284,7 +34297,7 @@
         <v>300</v>
       </c>
       <c r="N245" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B245, $C$2:$C$628, C245, $D$2:$D$628, D245, $E$2:$E$628, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -34330,7 +34343,7 @@
         <v>48320</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B246, $C$2:$C$628, C246, $D$2:$D$628, D246, $E$2:$E$628, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="36" t="s">
@@ -34380,7 +34393,7 @@
         <v>1000</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B247, $C$2:$C$628, C247, $D$2:$D$628, D247, $E$2:$E$628, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34414,7 +34427,7 @@
       </c>
       <c r="J248" s="32"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B248, $C$2:$C$628, C248, $D$2:$D$628, D248, $E$2:$E$628, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34453,7 +34466,7 @@
         <v>144</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B249, $C$2:$C$628, C249, $D$2:$D$628, D249, $E$2:$E$628, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34499,7 +34512,7 @@
         <v>300</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B250, $C$2:$C$628, C250, $D$2:$D$628, D250, $E$2:$E$628, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34545,7 +34558,7 @@
         <v>300</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B251, $C$2:$C$628, C251, $D$2:$D$628, D251, $E$2:$E$628, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="36" t="s">
@@ -34583,7 +34596,7 @@
       </c>
       <c r="J252" s="32"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B252, $C$2:$C$628, C252, $D$2:$D$628, D252, $E$2:$E$628, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P252" s="27"/>
@@ -34620,7 +34633,7 @@
         <v>116</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B253, $C$2:$C$628, C253, $D$2:$D$628, D253, $E$2:$E$628, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34666,7 +34679,7 @@
         <v>250</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B254, $C$2:$C$628, C254, $D$2:$D$628, D254, $E$2:$E$628, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="27"/>
@@ -34713,7 +34726,7 @@
         <v>450</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B255, $C$2:$C$628, C255, $D$2:$D$628, D255, $E$2:$E$628, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34759,7 +34772,7 @@
         <v>370</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B256, $C$2:$C$628, C256, $D$2:$D$628, D256, $E$2:$E$628, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P256" s="27"/>
@@ -34794,7 +34807,7 @@
       </c>
       <c r="J257" s="32"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B257, $C$2:$C$628, C257, $D$2:$D$628, D257, $E$2:$E$628, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="27"/>
@@ -34831,7 +34844,7 @@
         <v>117</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B258, $C$2:$C$628, C258, $D$2:$D$628, D258, $E$2:$E$628, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N323" si="10">IF(COUNTIFS( $B$2:$B$628, B258, $C$2:$C$628, C258, $D$2:$D$628, D258, $E$2:$E$628, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -34877,7 +34890,7 @@
         <v>47900</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B259, $C$2:$C$628, C259, $D$2:$D$628, D259, $E$2:$E$628, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="36" t="s">
@@ -34914,7 +34927,7 @@
       </c>
       <c r="J260" s="32"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B260, $C$2:$C$628, C260, $D$2:$D$628, D260, $E$2:$E$628, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34956,11 +34969,11 @@
         <v>25300</v>
       </c>
       <c r="M261" s="17">
-        <f t="shared" ref="M261:M266" si="6">ABS((D261*E261)-L261)</f>
+        <f t="shared" ref="M261:M266" si="11">ABS((D261*E261)-L261)</f>
         <v>650</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B261, $C$2:$C$628, C261, $D$2:$D$628, D261, $E$2:$E$628, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="36" t="s">
@@ -35005,11 +35018,11 @@
         <v>12480</v>
       </c>
       <c r="M262" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>495</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B262, $C$2:$C$628, C262, $D$2:$D$628, D262, $E$2:$E$628, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="36" t="s">
@@ -35054,11 +35067,11 @@
         <v>4200</v>
       </c>
       <c r="M263" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>290</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B263, $C$2:$C$628, C263, $D$2:$D$628, D263, $E$2:$E$628, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35100,11 +35113,11 @@
         <v>25780</v>
       </c>
       <c r="M264" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N264" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B264, $C$2:$C$628, C264, $D$2:$D$628, D264, $E$2:$E$628, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="36" t="s">
@@ -35150,11 +35163,11 @@
         <v>13300</v>
       </c>
       <c r="M265" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B265, $C$2:$C$628, C265, $D$2:$D$628, D265, $E$2:$E$628, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35196,11 +35209,11 @@
         <v>25800</v>
       </c>
       <c r="M266" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>1800</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B266, $C$2:$C$628, C266, $D$2:$D$628, D266, $E$2:$E$628, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35236,7 +35249,7 @@
         <v>116</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B267, $C$2:$C$628, C267, $D$2:$D$628, D267, $E$2:$E$628, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35282,7 +35295,7 @@
         <v>650</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B268, $C$2:$C$628, C268, $D$2:$D$628, D268, $E$2:$E$628, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O268"/>
@@ -35320,7 +35333,7 @@
         <v>116</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B269, $C$2:$C$628, C269, $D$2:$D$628, D269, $E$2:$E$628, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35356,7 +35369,7 @@
         <v>116</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B270, $C$2:$C$628, C270, $D$2:$D$628, D270, $E$2:$E$628, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35402,7 +35415,7 @@
         <v>47480</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B271, $C$2:$C$628, C271, $D$2:$D$628, D271, $E$2:$E$628, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35448,7 +35461,7 @@
         <v>450</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B272, $C$2:$C$628, C272, $D$2:$D$628, D272, $E$2:$E$628, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35494,7 +35507,7 @@
         <v>420</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B273, $C$2:$C$628, C273, $D$2:$D$628, D273, $E$2:$E$628, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35540,7 +35553,7 @@
         <v>340</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B274, $C$2:$C$628, C274, $D$2:$D$628, D274, $E$2:$E$628, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35586,7 +35599,7 @@
         <v>300</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B275, $C$2:$C$628, C275, $D$2:$D$628, D275, $E$2:$E$628, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35622,7 +35635,7 @@
         <v>116</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B276, $C$2:$C$628, C276, $D$2:$D$628, D276, $E$2:$E$628, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35656,7 +35669,7 @@
       </c>
       <c r="J277" s="32"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B277, $C$2:$C$628, C277, $D$2:$D$628, D277, $E$2:$E$628, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35702,7 +35715,7 @@
         <v>300</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B278, $C$2:$C$628, C278, $D$2:$D$628, D278, $E$2:$E$628, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35738,7 +35751,7 @@
         <v>116</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B279, $C$2:$C$628, C279, $D$2:$D$628, D279, $E$2:$E$628, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35784,7 +35797,7 @@
         <v>480</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B280, $C$2:$C$628, C280, $D$2:$D$628, D280, $E$2:$E$628, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35823,7 +35836,7 @@
       <c r="L281" s="16"/>
       <c r="M281" s="16"/>
       <c r="N281" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B281, $C$2:$C$628, C281, $D$2:$D$628, D281, $E$2:$E$628, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O281"/>
@@ -35870,7 +35883,7 @@
         <v>300</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B282, $C$2:$C$628, C282, $D$2:$D$628, D282, $E$2:$E$628, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35906,7 +35919,7 @@
         <v>117</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B283, $C$2:$C$628, C283, $D$2:$D$628, D283, $E$2:$E$628, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35942,7 +35955,7 @@
         <v>116</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B284, $C$2:$C$628, C284, $D$2:$D$628, D284, $E$2:$E$628, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35983,7 +35996,7 @@
       <c r="L285" s="16"/>
       <c r="M285" s="16"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B285, $C$2:$C$628, C285, $D$2:$D$628, D285, $E$2:$E$628, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36019,7 +36032,7 @@
         <v>116</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B286, $C$2:$C$628, C286, $D$2:$D$628, D286, $E$2:$E$628, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36055,7 +36068,7 @@
         <v>117</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B287, $C$2:$C$628, C287, $D$2:$D$628, D287, $E$2:$E$628, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36101,7 +36114,7 @@
         <v>285</v>
       </c>
       <c r="N288" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B288, $C$2:$C$628, C288, $D$2:$D$628, D288, $E$2:$E$628, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36147,7 +36160,7 @@
         <v>726</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B289, $C$2:$C$628, C289, $D$2:$D$628, D289, $E$2:$E$628, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36183,7 +36196,7 @@
         <v>152</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B290, $C$2:$C$628, C290, $D$2:$D$628, D290, $E$2:$E$628, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36219,7 +36232,7 @@
         <v>116</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B291, $C$2:$C$628, C291, $D$2:$D$628, D291, $E$2:$E$628, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36253,7 +36266,7 @@
       </c>
       <c r="J292" s="32"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B292, $C$2:$C$628, C292, $D$2:$D$628, D292, $E$2:$E$628, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36299,7 +36312,7 @@
         <v>275</v>
       </c>
       <c r="N293" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B293, $C$2:$C$628, C293, $D$2:$D$628, D293, $E$2:$E$628, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36345,7 +36358,7 @@
         <v>250</v>
       </c>
       <c r="N294" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B294, $C$2:$C$628, C294, $D$2:$D$628, D294, $E$2:$E$628, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36391,7 +36404,7 @@
         <v>250</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B295, $C$2:$C$628, C295, $D$2:$D$628, D295, $E$2:$E$628, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36425,7 +36438,7 @@
       </c>
       <c r="J296" s="32"/>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B296, $C$2:$C$628, C296, $D$2:$D$628, D296, $E$2:$E$628, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36471,7 +36484,7 @@
         <v>250</v>
       </c>
       <c r="N297" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B297, $C$2:$C$628, C297, $D$2:$D$628, D297, $E$2:$E$628, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P297" s="27"/>
@@ -36506,7 +36519,7 @@
       </c>
       <c r="J298" s="32"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B298, $C$2:$C$628, C298, $D$2:$D$628, D298, $E$2:$E$628, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36540,7 +36553,7 @@
       </c>
       <c r="J299" s="32"/>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B299, $C$2:$C$628, C299, $D$2:$D$628, D299, $E$2:$E$628, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36574,7 +36587,7 @@
       </c>
       <c r="J300" s="32"/>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B300, $C$2:$C$628, C300, $D$2:$D$628, D300, $E$2:$E$628, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36620,7 +36633,7 @@
         <v>300</v>
       </c>
       <c r="N301" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B301, $C$2:$C$628, C301, $D$2:$D$628, D301, $E$2:$E$628, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36656,7 +36669,7 @@
         <v>54</v>
       </c>
       <c r="N302" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B302, $C$2:$C$628, C302, $D$2:$D$628, D302, $E$2:$E$628, E302) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36692,7 +36705,7 @@
         <v>117</v>
       </c>
       <c r="N303" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B303, $C$2:$C$628, C303, $D$2:$D$628, D303, $E$2:$E$628, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36738,7 +36751,7 @@
         <v>235</v>
       </c>
       <c r="N304" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B304, $C$2:$C$628, C304, $D$2:$D$628, D304, $E$2:$E$628, E304) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36774,7 +36787,7 @@
         <v>117</v>
       </c>
       <c r="N305" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B305, $C$2:$C$628, C305, $D$2:$D$628, D305, $E$2:$E$628, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36808,7 +36821,7 @@
       </c>
       <c r="J306" s="32"/>
       <c r="N306" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B306, $C$2:$C$628, C306, $D$2:$D$628, D306, $E$2:$E$628, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36847,7 +36860,7 @@
       <c r="L307" s="25"/>
       <c r="M307" s="25"/>
       <c r="N307" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B307, $C$2:$C$628, C307, $D$2:$D$628, D307, $E$2:$E$628, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O307" s="27"/>
@@ -36888,7 +36901,7 @@
       <c r="L308" s="25"/>
       <c r="M308" s="25"/>
       <c r="N308" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B308, $C$2:$C$628, C308, $D$2:$D$628, D308, $E$2:$E$628, E308) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O308" s="27"/>
@@ -36936,7 +36949,7 @@
         <v>250</v>
       </c>
       <c r="N309" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B309, $C$2:$C$628, C309, $D$2:$D$628, D309, $E$2:$E$628, E309) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36972,7 +36985,7 @@
         <v>116</v>
       </c>
       <c r="N310" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B310, $C$2:$C$628, C310, $D$2:$D$628, D310, $E$2:$E$628, E310) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37010,7 +37023,7 @@
         <v>902.5</v>
       </c>
       <c r="N311" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B311, $C$2:$C$628, C311, $D$2:$D$628, D311, $E$2:$E$628, E311) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37044,11 +37057,11 @@
         <v>4036</v>
       </c>
       <c r="M312" s="17">
-        <f t="shared" ref="M312:M323" si="7">ABS((D312*E312)-L312)</f>
+        <f t="shared" ref="M312:M323" si="12">ABS((D312*E312)-L312)</f>
         <v>404</v>
       </c>
       <c r="N312" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B312, $C$2:$C$628, C312, $D$2:$D$628, D312, $E$2:$E$628, E312) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37082,11 +37095,11 @@
         <v>19154</v>
       </c>
       <c r="M313" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>840</v>
       </c>
       <c r="N313" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B313, $C$2:$C$628, C313, $D$2:$D$628, D313, $E$2:$E$628, E313) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37120,11 +37133,11 @@
         <v>11694</v>
       </c>
       <c r="M314" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="N314" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B314, $C$2:$C$628, C314, $D$2:$D$628, D314, $E$2:$E$628, E314) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37158,11 +37171,11 @@
         <v>9247.5</v>
       </c>
       <c r="M315" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>700</v>
       </c>
       <c r="N315" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B315, $C$2:$C$628, C315, $D$2:$D$628, D315, $E$2:$E$628, E315) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37196,11 +37209,11 @@
         <v>13237.5</v>
       </c>
       <c r="M316" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="N316" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B316, $C$2:$C$628, C316, $D$2:$D$628, D316, $E$2:$E$628, E316) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37234,11 +37247,11 @@
         <v>6126.75</v>
       </c>
       <c r="M317" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1028.25</v>
       </c>
       <c r="N317" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B317, $C$2:$C$628, C317, $D$2:$D$628, D317, $E$2:$E$628, E317) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37272,11 +37285,11 @@
         <v>16440</v>
       </c>
       <c r="M318" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="N318" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B318, $C$2:$C$628, C318, $D$2:$D$628, D318, $E$2:$E$628, E318) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37310,11 +37323,11 @@
         <v>34480</v>
       </c>
       <c r="M319" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>720</v>
       </c>
       <c r="N319" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B319, $C$2:$C$628, C319, $D$2:$D$628, D319, $E$2:$E$628, E319) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37348,11 +37361,11 @@
         <v>8422.5</v>
       </c>
       <c r="M320" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>277.5</v>
       </c>
       <c r="N320" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B320, $C$2:$C$628, C320, $D$2:$D$628, D320, $E$2:$E$628, E320) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37386,11 +37399,11 @@
         <v>33100</v>
       </c>
       <c r="M321" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>700</v>
       </c>
       <c r="N321" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B321, $C$2:$C$628, C321, $D$2:$D$628, D321, $E$2:$E$628, E321) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37424,11 +37437,11 @@
         <v>17087</v>
       </c>
       <c r="M322" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>393</v>
       </c>
       <c r="N322" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B322, $C$2:$C$628, C322, $D$2:$D$628, D322, $E$2:$E$628, E322) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -37462,11 +37475,11 @@
         <v>25500</v>
       </c>
       <c r="M323" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>660</v>
       </c>
       <c r="N323" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$628, B323, $C$2:$C$628, C323, $D$2:$D$628, D323, $E$2:$E$628, E323) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
